--- a/research/traditional_assets/database/data/argentina/argentina_retail_grocery_and_food.xlsx
+++ b/research/traditional_assets/database/data/argentina/argentina_retail_grocery_and_food.xlsx
@@ -1272,7 +1272,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -1409,22 +1409,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.1560040102215984</v>
+        <v>0.1554872461858228</v>
       </c>
       <c r="C2">
-        <v>944.2313313060241</v>
+        <v>939.1379716427325</v>
       </c>
       <c r="D2">
-        <v>891.8313313060241</v>
+        <v>896.0329716427325</v>
       </c>
       <c r="E2">
-        <v>-56.5</v>
+        <v>-47.205</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>9.295</v>
       </c>
       <c r="G2">
         <v>52.4</v>
@@ -1445,28 +1445,28 @@
         <v>56.95</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>0.4675385</v>
       </c>
       <c r="N2">
-        <v>56.95</v>
+        <v>56.4824615</v>
       </c>
       <c r="O2">
-        <v>19.9325</v>
+        <v>19.768861525</v>
       </c>
       <c r="P2">
-        <v>37.0175</v>
+        <v>36.713599975</v>
       </c>
       <c r="Q2">
-        <v>68.8175</v>
+        <v>68.51359997500001</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.1560040102215984</v>
+        <v>0.1567275719048715</v>
       </c>
       <c r="T2">
-        <v>0.5414733185171841</v>
+        <v>0.5450284463660343</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -1483,7 +1483,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>121.8081505587241</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -1491,22 +1491,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.1554872461858228</v>
+        <v>0.1549704821500472</v>
       </c>
       <c r="C3">
-        <v>939.1379716427325</v>
+        <v>934.0843893363696</v>
       </c>
       <c r="D3">
-        <v>896.0329716427325</v>
+        <v>900.2743893363696</v>
       </c>
       <c r="E3">
-        <v>-47.205</v>
+        <v>-37.91</v>
       </c>
       <c r="F3">
-        <v>9.295</v>
+        <v>18.59</v>
       </c>
       <c r="G3">
         <v>52.4</v>
@@ -1527,28 +1527,28 @@
         <v>56.95</v>
       </c>
       <c r="M3">
-        <v>0.4675385</v>
+        <v>0.9350769999999999</v>
       </c>
       <c r="N3">
-        <v>56.4824615</v>
+        <v>56.014923</v>
       </c>
       <c r="O3">
-        <v>19.768861525</v>
+        <v>19.60522305</v>
       </c>
       <c r="P3">
-        <v>36.713599975</v>
+        <v>36.40969995</v>
       </c>
       <c r="Q3">
-        <v>68.51359997500001</v>
+        <v>68.20969995</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.1567275719048715</v>
+        <v>0.1574659001531094</v>
       </c>
       <c r="T3">
-        <v>0.5450284463660343</v>
+        <v>0.5486561278444528</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -1565,7 +1565,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>121.8081505587241</v>
+        <v>60.90407527936203</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -1573,22 +1573,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.1549704821500472</v>
+        <v>0.1544537181142716</v>
       </c>
       <c r="C4">
-        <v>934.0843893363696</v>
+        <v>929.0711519378997</v>
       </c>
       <c r="D4">
-        <v>900.2743893363696</v>
+        <v>904.5561519378997</v>
       </c>
       <c r="E4">
-        <v>-37.91</v>
+        <v>-28.615</v>
       </c>
       <c r="F4">
-        <v>18.59</v>
+        <v>27.885</v>
       </c>
       <c r="G4">
         <v>52.4</v>
@@ -1609,28 +1609,28 @@
         <v>56.95</v>
       </c>
       <c r="M4">
-        <v>0.9350769999999999</v>
+        <v>1.4026155</v>
       </c>
       <c r="N4">
-        <v>56.014923</v>
+        <v>55.5473845</v>
       </c>
       <c r="O4">
-        <v>19.60522305</v>
+        <v>19.441584575</v>
       </c>
       <c r="P4">
-        <v>36.40969995</v>
+        <v>36.105799925</v>
       </c>
       <c r="Q4">
-        <v>68.20969995</v>
+        <v>67.905799925</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.1574659001531094</v>
+        <v>0.1582194516641975</v>
       </c>
       <c r="T4">
-        <v>0.5486561278444528</v>
+        <v>0.5523586068791274</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -1647,7 +1647,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>60.90407527936203</v>
+        <v>40.60271685290802</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -1655,22 +1655,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.1544537181142716</v>
+        <v>0.153936954078496</v>
       </c>
       <c r="C5">
-        <v>929.0711519378997</v>
+        <v>924.0988378471196</v>
       </c>
       <c r="D5">
-        <v>904.5561519378997</v>
+        <v>908.8788378471196</v>
       </c>
       <c r="E5">
-        <v>-28.615</v>
+        <v>-19.32</v>
       </c>
       <c r="F5">
-        <v>27.885</v>
+        <v>37.18</v>
       </c>
       <c r="G5">
         <v>52.4</v>
@@ -1691,28 +1691,28 @@
         <v>56.95</v>
       </c>
       <c r="M5">
-        <v>1.4026155</v>
+        <v>1.870154</v>
       </c>
       <c r="N5">
-        <v>55.5473845</v>
+        <v>55.079846</v>
       </c>
       <c r="O5">
-        <v>19.441584575</v>
+        <v>19.2779461</v>
       </c>
       <c r="P5">
-        <v>36.105799925</v>
+        <v>35.8018999</v>
       </c>
       <c r="Q5">
-        <v>67.905799925</v>
+        <v>67.60189990000001</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.1582194516641975</v>
+        <v>0.1589887021651</v>
       </c>
       <c r="T5">
-        <v>0.5523586068791274</v>
+        <v>0.5561382208936911</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -1729,7 +1729,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>40.60271685290802</v>
+        <v>30.45203763968101</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -1737,22 +1737,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.153936954078496</v>
+        <v>0.1534201900427204</v>
       </c>
       <c r="C6">
-        <v>924.0988378471196</v>
+        <v>919.1680365731253</v>
       </c>
       <c r="D6">
-        <v>908.8788378471196</v>
+        <v>913.2430365731253</v>
       </c>
       <c r="E6">
-        <v>-19.32</v>
+        <v>-10.025</v>
       </c>
       <c r="F6">
-        <v>37.18</v>
+        <v>46.475</v>
       </c>
       <c r="G6">
         <v>52.4</v>
@@ -1773,28 +1773,28 @@
         <v>56.95</v>
       </c>
       <c r="M6">
-        <v>1.870154</v>
+        <v>2.3376925</v>
       </c>
       <c r="N6">
-        <v>55.079846</v>
+        <v>54.6123075</v>
       </c>
       <c r="O6">
-        <v>19.2779461</v>
+        <v>19.114307625</v>
       </c>
       <c r="P6">
-        <v>35.8018999</v>
+        <v>35.497999875</v>
       </c>
       <c r="Q6">
-        <v>67.60189990000001</v>
+        <v>67.297999875</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.1589887021651</v>
+        <v>0.1597741474133899</v>
       </c>
       <c r="T6">
-        <v>0.5561382208936911</v>
+        <v>0.559997405729614</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -1811,7 +1811,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>30.45203763968101</v>
+        <v>24.36163011174481</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -1819,22 +1819,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.1534201900427204</v>
+        <v>0.1529034260069448</v>
       </c>
       <c r="C7">
-        <v>919.1680365731253</v>
+        <v>914.2793490023173</v>
       </c>
       <c r="D7">
-        <v>913.2430365731253</v>
+        <v>917.6493490023173</v>
       </c>
       <c r="E7">
-        <v>-10.025</v>
+        <v>-0.7299999999999969</v>
       </c>
       <c r="F7">
-        <v>46.475</v>
+        <v>55.77</v>
       </c>
       <c r="G7">
         <v>52.4</v>
@@ -1855,28 +1855,28 @@
         <v>56.95</v>
       </c>
       <c r="M7">
-        <v>2.3376925</v>
+        <v>2.805231</v>
       </c>
       <c r="N7">
-        <v>54.6123075</v>
+        <v>54.144769</v>
       </c>
       <c r="O7">
-        <v>19.114307625</v>
+        <v>18.95066915</v>
       </c>
       <c r="P7">
-        <v>35.497999875</v>
+        <v>35.19409985</v>
       </c>
       <c r="Q7">
-        <v>67.297999875</v>
+        <v>66.99409985</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.1597741474133899</v>
+        <v>0.1605763042627073</v>
       </c>
       <c r="T7">
-        <v>0.559997405729614</v>
+        <v>0.5639387008811949</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -1893,7 +1893,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>24.36163011174481</v>
+        <v>20.30135842645401</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -1901,22 +1901,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.1529034260069448</v>
+        <v>0.1523866619711692</v>
       </c>
       <c r="C8">
-        <v>914.2793490023173</v>
+        <v>909.4333876742064</v>
       </c>
       <c r="D8">
-        <v>917.6493490023173</v>
+        <v>922.0983876742065</v>
       </c>
       <c r="E8">
-        <v>-0.730000000000004</v>
+        <v>8.564999999999998</v>
       </c>
       <c r="F8">
-        <v>55.77</v>
+        <v>65.065</v>
       </c>
       <c r="G8">
         <v>52.4</v>
@@ -1937,28 +1937,28 @@
         <v>56.95</v>
       </c>
       <c r="M8">
-        <v>2.805231</v>
+        <v>3.2727695</v>
       </c>
       <c r="N8">
-        <v>54.144769</v>
+        <v>53.6772305</v>
       </c>
       <c r="O8">
-        <v>18.95066915</v>
+        <v>18.787030675</v>
       </c>
       <c r="P8">
-        <v>35.19409985</v>
+        <v>34.890199825</v>
       </c>
       <c r="Q8">
-        <v>66.99409985</v>
+        <v>66.69019982499999</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.1605763042627073</v>
+        <v>0.1613957117969562</v>
       </c>
       <c r="T8">
-        <v>0.5639387008811949</v>
+        <v>0.5679647550682936</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -1975,7 +1975,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>20.30135842645401</v>
+        <v>17.40116436553201</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -1983,22 +1983,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.1523866619711692</v>
+        <v>0.1518698979353937</v>
       </c>
       <c r="C9">
-        <v>909.4333876742064</v>
+        <v>904.6307770652747</v>
       </c>
       <c r="D9">
-        <v>922.0983876742065</v>
+        <v>926.5907770652748</v>
       </c>
       <c r="E9">
-        <v>8.565000000000012</v>
+        <v>17.86</v>
       </c>
       <c r="F9">
-        <v>65.06500000000001</v>
+        <v>74.36</v>
       </c>
       <c r="G9">
         <v>52.4</v>
@@ -2019,28 +2019,28 @@
         <v>56.95</v>
       </c>
       <c r="M9">
-        <v>3.2727695</v>
+        <v>3.740308</v>
       </c>
       <c r="N9">
-        <v>53.6772305</v>
+        <v>53.209692</v>
       </c>
       <c r="O9">
-        <v>18.787030675</v>
+        <v>18.6233922</v>
       </c>
       <c r="P9">
-        <v>34.890199825</v>
+        <v>34.58629980000001</v>
       </c>
       <c r="Q9">
-        <v>66.69019982499999</v>
+        <v>66.3862998</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.1613957117969562</v>
+        <v>0.1622329325384713</v>
       </c>
       <c r="T9">
-        <v>0.5679647550682936</v>
+        <v>0.5720783321725031</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -2057,7 +2057,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>17.401164365532</v>
+        <v>15.22601881984051</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -2065,22 +2065,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.1518698979353937</v>
+        <v>0.151353133899618</v>
       </c>
       <c r="C10">
-        <v>904.6307770652747</v>
+        <v>899.8721538811836</v>
       </c>
       <c r="D10">
-        <v>926.5907770652748</v>
+        <v>931.1271538811836</v>
       </c>
       <c r="E10">
-        <v>17.86</v>
+        <v>27.155</v>
       </c>
       <c r="F10">
-        <v>74.36</v>
+        <v>83.655</v>
       </c>
       <c r="G10">
         <v>52.4</v>
@@ -2101,28 +2101,28 @@
         <v>56.95</v>
       </c>
       <c r="M10">
-        <v>3.740308</v>
+        <v>4.2078465</v>
       </c>
       <c r="N10">
-        <v>53.209692</v>
+        <v>52.7421535</v>
       </c>
       <c r="O10">
-        <v>18.6233922</v>
+        <v>18.459753725</v>
       </c>
       <c r="P10">
-        <v>34.58629980000001</v>
+        <v>34.282399775</v>
       </c>
       <c r="Q10">
-        <v>66.3862998</v>
+        <v>66.082399775</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.1622329325384713</v>
+        <v>0.163088553735844</v>
       </c>
       <c r="T10">
-        <v>0.5720783321725031</v>
+        <v>0.5762823175647173</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -2139,7 +2139,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>15.22601881984051</v>
+        <v>13.53423895096934</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -2147,22 +2147,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.151353133899618</v>
+        <v>0.1509338698638425</v>
       </c>
       <c r="C11">
-        <v>899.8721538811836</v>
+        <v>894.2904018464874</v>
       </c>
       <c r="D11">
-        <v>931.1271538811836</v>
+        <v>934.8404018464873</v>
       </c>
       <c r="E11">
-        <v>27.155</v>
+        <v>36.44999999999999</v>
       </c>
       <c r="F11">
-        <v>83.655</v>
+        <v>92.94999999999999</v>
       </c>
       <c r="G11">
         <v>52.4</v>
@@ -2183,45 +2183,45 @@
         <v>56.95</v>
       </c>
       <c r="M11">
-        <v>4.2078465</v>
+        <v>4.81481</v>
       </c>
       <c r="N11">
-        <v>52.7421535</v>
+        <v>52.13519</v>
       </c>
       <c r="O11">
-        <v>18.459753725</v>
+        <v>18.2473165</v>
       </c>
       <c r="P11">
-        <v>34.282399775</v>
+        <v>33.8878735</v>
       </c>
       <c r="Q11">
-        <v>66.082399775</v>
+        <v>65.68787349999999</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.163088553735844</v>
+        <v>0.1639631887376027</v>
       </c>
       <c r="T11">
-        <v>0.5762823175647173</v>
+        <v>0.5805797248545362</v>
       </c>
       <c r="U11">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V11">
         <v>0.35</v>
       </c>
       <c r="W11">
-        <v>0.032695</v>
+        <v>0.03367</v>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y11">
-        <v>13.53423895096934</v>
+        <v>11.82808875116567</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -2229,22 +2229,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.1509338698638425</v>
+        <v>0.1504268558280669</v>
       </c>
       <c r="C12">
-        <v>894.2904018464873</v>
+        <v>889.5255695667632</v>
       </c>
       <c r="D12">
-        <v>934.8404018464873</v>
+        <v>939.3705695667633</v>
       </c>
       <c r="E12">
-        <v>36.45</v>
+        <v>45.745</v>
       </c>
       <c r="F12">
-        <v>92.95</v>
+        <v>102.245</v>
       </c>
       <c r="G12">
         <v>52.4</v>
@@ -2265,28 +2265,28 @@
         <v>56.95</v>
       </c>
       <c r="M12">
-        <v>4.81481</v>
+        <v>5.296291</v>
       </c>
       <c r="N12">
-        <v>52.13519</v>
+        <v>51.65370900000001</v>
       </c>
       <c r="O12">
-        <v>18.2473165</v>
+        <v>18.07879815</v>
       </c>
       <c r="P12">
-        <v>33.8878735</v>
+        <v>33.57491085000001</v>
       </c>
       <c r="Q12">
-        <v>65.68787349999999</v>
+        <v>65.37491085000001</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.1639631887376027</v>
+        <v>0.1648574784585021</v>
       </c>
       <c r="T12">
-        <v>0.5805797248545362</v>
+        <v>0.5849737030946882</v>
       </c>
       <c r="U12">
         <v>0.0518</v>
@@ -2303,7 +2303,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>11.82808875116567</v>
+        <v>10.75280795560516</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -2311,22 +2311,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.1504268558280669</v>
+        <v>0.1499198417922913</v>
       </c>
       <c r="C13">
-        <v>889.5255695667632</v>
+        <v>884.8048568050688</v>
       </c>
       <c r="D13">
-        <v>939.3705695667633</v>
+        <v>943.9448568050688</v>
       </c>
       <c r="E13">
-        <v>45.745</v>
+        <v>55.03999999999999</v>
       </c>
       <c r="F13">
-        <v>102.245</v>
+        <v>111.54</v>
       </c>
       <c r="G13">
         <v>52.4</v>
@@ -2347,28 +2347,28 @@
         <v>56.95</v>
       </c>
       <c r="M13">
-        <v>5.296291</v>
+        <v>5.777772</v>
       </c>
       <c r="N13">
-        <v>51.65370900000001</v>
+        <v>51.172228</v>
       </c>
       <c r="O13">
-        <v>18.07879815</v>
+        <v>17.9102798</v>
       </c>
       <c r="P13">
-        <v>33.57491085000001</v>
+        <v>33.26194820000001</v>
       </c>
       <c r="Q13">
-        <v>65.37491085000001</v>
+        <v>65.0619482</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1648574784585021</v>
+        <v>0.1657720929457855</v>
       </c>
       <c r="T13">
-        <v>0.5849737030946882</v>
+        <v>0.5894675444766617</v>
       </c>
       <c r="U13">
         <v>0.0518</v>
@@ -2385,7 +2385,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>10.75280795560516</v>
+        <v>9.856740625971396</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -2393,22 +2393,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.1499198417922913</v>
+        <v>0.1495564777565156</v>
       </c>
       <c r="C14">
-        <v>884.8048568050688</v>
+        <v>878.8156322143232</v>
       </c>
       <c r="D14">
-        <v>943.9448568050688</v>
+        <v>947.2506322143232</v>
       </c>
       <c r="E14">
-        <v>55.03999999999999</v>
+        <v>64.33500000000001</v>
       </c>
       <c r="F14">
-        <v>111.54</v>
+        <v>120.835</v>
       </c>
       <c r="G14">
         <v>52.4</v>
@@ -2429,45 +2429,45 @@
         <v>56.95</v>
       </c>
       <c r="M14">
-        <v>5.777772</v>
+        <v>6.464672500000001</v>
       </c>
       <c r="N14">
-        <v>51.172228</v>
+        <v>50.4853275</v>
       </c>
       <c r="O14">
-        <v>17.9102798</v>
+        <v>17.669864625</v>
       </c>
       <c r="P14">
-        <v>33.26194820000001</v>
+        <v>32.81546287500001</v>
       </c>
       <c r="Q14">
-        <v>65.0619482</v>
+        <v>64.61546287500001</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1657720929457855</v>
+        <v>0.1667077330534663</v>
       </c>
       <c r="T14">
-        <v>0.5894675444766617</v>
+        <v>0.5940646925570714</v>
       </c>
       <c r="U14">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V14">
         <v>0.35</v>
       </c>
       <c r="W14">
-        <v>0.03367</v>
+        <v>0.034775</v>
       </c>
       <c r="X14" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y14">
-        <v>9.856740625971396</v>
+        <v>8.809417646446899</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -2475,22 +2475,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.1495564777565156</v>
+        <v>0.1490605137207401</v>
       </c>
       <c r="C15">
-        <v>878.8156322143232</v>
+        <v>874.0703117531497</v>
       </c>
       <c r="D15">
-        <v>947.2506322143232</v>
+        <v>951.8003117531497</v>
       </c>
       <c r="E15">
-        <v>64.33500000000001</v>
+        <v>73.63000000000002</v>
       </c>
       <c r="F15">
-        <v>120.835</v>
+        <v>130.13</v>
       </c>
       <c r="G15">
         <v>52.4</v>
@@ -2511,28 +2511,28 @@
         <v>56.95</v>
       </c>
       <c r="M15">
-        <v>6.464672500000001</v>
+        <v>6.961955000000001</v>
       </c>
       <c r="N15">
-        <v>50.4853275</v>
+        <v>49.988045</v>
       </c>
       <c r="O15">
-        <v>17.669864625</v>
+        <v>17.49581575</v>
       </c>
       <c r="P15">
-        <v>32.81546287500001</v>
+        <v>32.49222925</v>
       </c>
       <c r="Q15">
-        <v>64.61546287500001</v>
+        <v>64.29222924999999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.1667077330534663</v>
+        <v>0.1676651322334187</v>
       </c>
       <c r="T15">
-        <v>0.5940646925570714</v>
+        <v>0.5987687510579559</v>
       </c>
       <c r="U15">
         <v>0.0535</v>
@@ -2549,7 +2549,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>8.809417646446899</v>
+        <v>8.180173528843548</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -2557,22 +2557,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.1490605137207401</v>
+        <v>0.1485645496849645</v>
       </c>
       <c r="C16">
-        <v>874.0703117531497</v>
+        <v>869.3689067751363</v>
       </c>
       <c r="D16">
-        <v>951.8003117531497</v>
+        <v>956.3939067751364</v>
       </c>
       <c r="E16">
-        <v>73.63000000000002</v>
+        <v>82.92500000000001</v>
       </c>
       <c r="F16">
-        <v>130.13</v>
+        <v>139.425</v>
       </c>
       <c r="G16">
         <v>52.4</v>
@@ -2593,28 +2593,28 @@
         <v>56.95</v>
       </c>
       <c r="M16">
-        <v>6.961955000000001</v>
+        <v>7.4592375</v>
       </c>
       <c r="N16">
-        <v>49.988045</v>
+        <v>49.4907625</v>
       </c>
       <c r="O16">
-        <v>17.49581575</v>
+        <v>17.321766875</v>
       </c>
       <c r="P16">
-        <v>32.49222925</v>
+        <v>32.16899562500001</v>
       </c>
       <c r="Q16">
-        <v>64.29222924999999</v>
+        <v>63.96899562500001</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1676651322334187</v>
+        <v>0.1686450584528994</v>
       </c>
       <c r="T16">
-        <v>0.5987687510579559</v>
+        <v>0.6035834932882729</v>
       </c>
       <c r="U16">
         <v>0.0535</v>
@@ -2631,7 +2631,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>8.180173528843548</v>
+        <v>7.634828626920647</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -2639,22 +2639,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.1485645496849645</v>
+        <v>0.1481517856491889</v>
       </c>
       <c r="C17">
-        <v>869.3689067751365</v>
+        <v>863.9308498294058</v>
       </c>
       <c r="D17">
-        <v>956.3939067751364</v>
+        <v>960.2508498294059</v>
       </c>
       <c r="E17">
-        <v>82.92499999999998</v>
+        <v>92.22</v>
       </c>
       <c r="F17">
-        <v>139.425</v>
+        <v>148.72</v>
       </c>
       <c r="G17">
         <v>52.4</v>
@@ -2675,45 +2675,45 @@
         <v>56.95</v>
       </c>
       <c r="M17">
-        <v>7.459237499999999</v>
+        <v>8.075495999999999</v>
       </c>
       <c r="N17">
-        <v>49.4907625</v>
+        <v>48.874504</v>
       </c>
       <c r="O17">
-        <v>17.321766875</v>
+        <v>17.1060764</v>
       </c>
       <c r="P17">
-        <v>32.16899562500001</v>
+        <v>31.7684276</v>
       </c>
       <c r="Q17">
-        <v>63.96899562500001</v>
+        <v>63.5684276</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1686450584528994</v>
+        <v>0.1696483162490344</v>
       </c>
       <c r="T17">
-        <v>0.6035834932882729</v>
+        <v>0.6085128722383593</v>
       </c>
       <c r="U17">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V17">
         <v>0.35</v>
       </c>
       <c r="W17">
-        <v>0.034775</v>
+        <v>0.035295</v>
       </c>
       <c r="X17" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y17">
-        <v>7.634828626920648</v>
+        <v>7.052198403664618</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -2721,22 +2721,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.1481517856491889</v>
+        <v>0.1476610216134133</v>
       </c>
       <c r="C18">
-        <v>863.9308498294058</v>
+        <v>859.2623161160656</v>
       </c>
       <c r="D18">
-        <v>960.2508498294059</v>
+        <v>964.8773161160656</v>
       </c>
       <c r="E18">
-        <v>92.22</v>
+        <v>101.515</v>
       </c>
       <c r="F18">
-        <v>148.72</v>
+        <v>158.015</v>
       </c>
       <c r="G18">
         <v>52.4</v>
@@ -2757,28 +2757,28 @@
         <v>56.95</v>
       </c>
       <c r="M18">
-        <v>8.075495999999999</v>
+        <v>8.5802145</v>
       </c>
       <c r="N18">
-        <v>48.874504</v>
+        <v>48.36978550000001</v>
       </c>
       <c r="O18">
-        <v>17.1060764</v>
+        <v>16.929424925</v>
       </c>
       <c r="P18">
-        <v>31.7684276</v>
+        <v>31.44036057500001</v>
       </c>
       <c r="Q18">
-        <v>63.5684276</v>
+        <v>63.240360575</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.1696483162490344</v>
+        <v>0.1706757489318233</v>
       </c>
       <c r="T18">
-        <v>0.6085128722383593</v>
+        <v>0.6135610314041104</v>
       </c>
       <c r="U18">
         <v>0.0543</v>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="Y18">
-        <v>7.052198403664618</v>
+        <v>6.637363203449052</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -2803,22 +2803,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.1476610216134133</v>
+        <v>0.1471702575776377</v>
       </c>
       <c r="C19">
-        <v>859.2623161160656</v>
+        <v>854.6385786441579</v>
       </c>
       <c r="D19">
-        <v>964.8773161160656</v>
+        <v>969.5485786441579</v>
       </c>
       <c r="E19">
-        <v>101.515</v>
+        <v>110.81</v>
       </c>
       <c r="F19">
-        <v>158.015</v>
+        <v>167.31</v>
       </c>
       <c r="G19">
         <v>52.4</v>
@@ -2839,28 +2839,28 @@
         <v>56.95</v>
       </c>
       <c r="M19">
-        <v>8.5802145</v>
+        <v>9.084933000000001</v>
       </c>
       <c r="N19">
-        <v>48.36978550000001</v>
+        <v>47.865067</v>
       </c>
       <c r="O19">
-        <v>16.929424925</v>
+        <v>16.75277345</v>
       </c>
       <c r="P19">
-        <v>31.44036057500001</v>
+        <v>31.11229355</v>
       </c>
       <c r="Q19">
-        <v>63.240360575</v>
+        <v>62.91229355</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1706757489318233</v>
+        <v>0.1717282409483387</v>
       </c>
       <c r="T19">
-        <v>0.6135610314041104</v>
+        <v>0.6187323164031725</v>
       </c>
       <c r="U19">
         <v>0.0543</v>
@@ -2877,7 +2877,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>6.637363203449052</v>
+        <v>6.268620803257437</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -2885,22 +2885,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.1471702575776377</v>
+        <v>0.1468029935418621</v>
       </c>
       <c r="C20">
-        <v>854.6385786441576</v>
+        <v>848.8690219145669</v>
       </c>
       <c r="D20">
-        <v>969.5485786441577</v>
+        <v>973.0740219145669</v>
       </c>
       <c r="E20">
-        <v>110.81</v>
+        <v>120.105</v>
       </c>
       <c r="F20">
-        <v>167.31</v>
+        <v>176.605</v>
       </c>
       <c r="G20">
         <v>52.4</v>
@@ -2921,45 +2921,45 @@
         <v>56.95</v>
       </c>
       <c r="M20">
-        <v>9.084932999999999</v>
+        <v>9.766256499999999</v>
       </c>
       <c r="N20">
-        <v>47.865067</v>
+        <v>47.18374350000001</v>
       </c>
       <c r="O20">
-        <v>16.75277345</v>
+        <v>16.514310225</v>
       </c>
       <c r="P20">
-        <v>31.11229355</v>
+        <v>30.669433275</v>
       </c>
       <c r="Q20">
-        <v>62.91229355</v>
+        <v>62.469433275</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1717282409483387</v>
+        <v>0.172806720422052</v>
       </c>
       <c r="T20">
-        <v>0.6187323164031725</v>
+        <v>0.6240312874515943</v>
       </c>
       <c r="U20">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V20">
         <v>0.35</v>
       </c>
       <c r="W20">
-        <v>0.035295</v>
+        <v>0.035945</v>
       </c>
       <c r="X20" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y20">
-        <v>6.268620803257438</v>
+        <v>5.831302915298202</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -2967,22 +2967,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.1468029935418621</v>
+        <v>0.1463187295060865</v>
       </c>
       <c r="C21">
-        <v>848.8690219145669</v>
+        <v>844.2619517687957</v>
       </c>
       <c r="D21">
-        <v>973.0740219145669</v>
+        <v>977.7619517687956</v>
       </c>
       <c r="E21">
-        <v>120.105</v>
+        <v>129.4</v>
       </c>
       <c r="F21">
-        <v>176.605</v>
+        <v>185.9</v>
       </c>
       <c r="G21">
         <v>52.4</v>
@@ -3003,28 +3003,28 @@
         <v>56.95</v>
       </c>
       <c r="M21">
-        <v>9.766256499999999</v>
+        <v>10.28027</v>
       </c>
       <c r="N21">
-        <v>47.18374350000001</v>
+        <v>46.66973</v>
       </c>
       <c r="O21">
-        <v>16.514310225</v>
+        <v>16.3344055</v>
       </c>
       <c r="P21">
-        <v>30.669433275</v>
+        <v>30.3353245</v>
       </c>
       <c r="Q21">
-        <v>62.469433275</v>
+        <v>62.1353245</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.172806720422052</v>
+        <v>0.1739121618826082</v>
       </c>
       <c r="T21">
-        <v>0.6240312874515943</v>
+        <v>0.6294627327762266</v>
       </c>
       <c r="U21">
         <v>0.0553</v>
@@ -3041,7 +3041,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>5.831302915298202</v>
+        <v>5.539737769533291</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -3049,22 +3049,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.1463187295060865</v>
+        <v>0.145834465470311</v>
       </c>
       <c r="C22">
-        <v>844.2619517687957</v>
+        <v>839.7002698963555</v>
       </c>
       <c r="D22">
-        <v>977.7619517687956</v>
+        <v>982.4952698963555</v>
       </c>
       <c r="E22">
-        <v>129.4</v>
+        <v>138.695</v>
       </c>
       <c r="F22">
-        <v>185.9</v>
+        <v>195.195</v>
       </c>
       <c r="G22">
         <v>52.4</v>
@@ -3085,28 +3085,28 @@
         <v>56.95</v>
       </c>
       <c r="M22">
-        <v>10.28027</v>
+        <v>10.7942835</v>
       </c>
       <c r="N22">
-        <v>46.66973</v>
+        <v>46.1557165</v>
       </c>
       <c r="O22">
-        <v>16.3344055</v>
+        <v>16.154500775</v>
       </c>
       <c r="P22">
-        <v>30.3353245</v>
+        <v>30.001215725</v>
       </c>
       <c r="Q22">
-        <v>62.1353245</v>
+        <v>61.80121572499999</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1739121618826082</v>
+        <v>0.1750455892029252</v>
       </c>
       <c r="T22">
-        <v>0.6294627327762266</v>
+        <v>0.6350316830457862</v>
       </c>
       <c r="U22">
         <v>0.0553</v>
@@ -3123,7 +3123,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>5.539737769533291</v>
+        <v>5.275940732888847</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -3131,22 +3131,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.145834465470311</v>
+        <v>0.1453502014345353</v>
       </c>
       <c r="C23">
-        <v>839.7002698963556</v>
+        <v>835.1846386738596</v>
       </c>
       <c r="D23">
-        <v>982.4952698963555</v>
+        <v>987.2746386738596</v>
       </c>
       <c r="E23">
-        <v>138.695</v>
+        <v>147.99</v>
       </c>
       <c r="F23">
-        <v>195.195</v>
+        <v>204.49</v>
       </c>
       <c r="G23">
         <v>52.4</v>
@@ -3167,28 +3167,28 @@
         <v>56.95</v>
       </c>
       <c r="M23">
-        <v>10.7942835</v>
+        <v>11.308297</v>
       </c>
       <c r="N23">
-        <v>46.1557165</v>
+        <v>45.641703</v>
       </c>
       <c r="O23">
-        <v>16.154500775</v>
+        <v>15.97459605</v>
       </c>
       <c r="P23">
-        <v>30.00121572500001</v>
+        <v>29.66710695</v>
       </c>
       <c r="Q23">
-        <v>61.80121572500001</v>
+        <v>61.46710695</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1750455892029252</v>
+        <v>0.1762080787622248</v>
       </c>
       <c r="T23">
-        <v>0.6350316830457862</v>
+        <v>0.6407434269120011</v>
       </c>
       <c r="U23">
         <v>0.0553</v>
@@ -3205,7 +3205,7 @@
         </is>
       </c>
       <c r="Y23">
-        <v>5.275940732888849</v>
+        <v>5.036125245030264</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -3213,22 +3213,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.1453502014345353</v>
+        <v>0.1448659373987597</v>
       </c>
       <c r="C24">
-        <v>835.1846386738596</v>
+        <v>830.7157334295033</v>
       </c>
       <c r="D24">
-        <v>987.2746386738596</v>
+        <v>992.1007334295033</v>
       </c>
       <c r="E24">
-        <v>147.99</v>
+        <v>157.285</v>
       </c>
       <c r="F24">
-        <v>204.49</v>
+        <v>213.785</v>
       </c>
       <c r="G24">
         <v>52.4</v>
@@ -3249,28 +3249,28 @@
         <v>56.95</v>
       </c>
       <c r="M24">
-        <v>11.308297</v>
+        <v>11.8223105</v>
       </c>
       <c r="N24">
-        <v>45.641703</v>
+        <v>45.1276895</v>
       </c>
       <c r="O24">
-        <v>15.97459605</v>
+        <v>15.794691325</v>
       </c>
       <c r="P24">
-        <v>29.66710695</v>
+        <v>29.332998175</v>
       </c>
       <c r="Q24">
-        <v>61.46710695</v>
+        <v>61.132998175</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1762080787622248</v>
+        <v>0.1774007628555321</v>
       </c>
       <c r="T24">
-        <v>0.6407434269120011</v>
+        <v>0.6466035277617542</v>
       </c>
       <c r="U24">
         <v>0.0553</v>
@@ -3287,7 +3287,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>5.036125245030264</v>
+        <v>4.817163277855036</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -3295,22 +3295,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.1448659373987597</v>
+        <v>0.1443816733629841</v>
       </c>
       <c r="C25">
-        <v>830.7157334295033</v>
+        <v>826.2942427611771</v>
       </c>
       <c r="D25">
-        <v>992.1007334295033</v>
+        <v>996.974242761177</v>
       </c>
       <c r="E25">
-        <v>157.285</v>
+        <v>166.58</v>
       </c>
       <c r="F25">
-        <v>213.785</v>
+        <v>223.08</v>
       </c>
       <c r="G25">
         <v>52.4</v>
@@ -3331,28 +3331,28 @@
         <v>56.95</v>
       </c>
       <c r="M25">
-        <v>11.8223105</v>
+        <v>12.336324</v>
       </c>
       <c r="N25">
-        <v>45.1276895</v>
+        <v>44.613676</v>
       </c>
       <c r="O25">
-        <v>15.794691325</v>
+        <v>15.6147866</v>
       </c>
       <c r="P25">
-        <v>29.332998175</v>
+        <v>28.9988894</v>
       </c>
       <c r="Q25">
-        <v>61.132998175</v>
+        <v>60.79888939999999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1774007628555321</v>
+        <v>0.1786248333723476</v>
       </c>
       <c r="T25">
-        <v>0.6466035277617542</v>
+        <v>0.652617841791764</v>
       </c>
       <c r="U25">
         <v>0.0553</v>
@@ -3369,7 +3369,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>4.817163277855036</v>
+        <v>4.616448141277742</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -3377,22 +3377,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.1443816733629841</v>
+        <v>0.1443036593272086</v>
       </c>
       <c r="C26">
-        <v>826.2942427611772</v>
+        <v>817.7888376328124</v>
       </c>
       <c r="D26">
-        <v>996.974242761177</v>
+        <v>997.7638376328124</v>
       </c>
       <c r="E26">
-        <v>166.58</v>
+        <v>175.875</v>
       </c>
       <c r="F26">
-        <v>223.08</v>
+        <v>232.375</v>
       </c>
       <c r="G26">
         <v>52.4</v>
@@ -3413,45 +3413,45 @@
         <v>56.95</v>
       </c>
       <c r="M26">
-        <v>12.336324</v>
+        <v>13.431275</v>
       </c>
       <c r="N26">
-        <v>44.61367600000001</v>
+        <v>43.518725</v>
       </c>
       <c r="O26">
-        <v>15.6147866</v>
+        <v>15.23155375</v>
       </c>
       <c r="P26">
-        <v>28.9988894</v>
+        <v>28.28717125</v>
       </c>
       <c r="Q26">
-        <v>60.7988894</v>
+        <v>60.08717125</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1786248333723476</v>
+        <v>0.1798815457696114</v>
       </c>
       <c r="T26">
-        <v>0.652617841791764</v>
+        <v>0.6587925375292407</v>
       </c>
       <c r="U26">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V26">
         <v>0.35</v>
       </c>
       <c r="W26">
-        <v>0.035945</v>
+        <v>0.03757000000000001</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y26">
-        <v>4.616448141277743</v>
+        <v>4.2401037876151</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -3459,22 +3459,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.1443036593272086</v>
+        <v>0.1438356452914329</v>
       </c>
       <c r="C27">
-        <v>817.7888376328124</v>
+        <v>813.257079400777</v>
       </c>
       <c r="D27">
-        <v>997.7638376328124</v>
+        <v>1002.527079400777</v>
       </c>
       <c r="E27">
-        <v>175.875</v>
+        <v>185.17</v>
       </c>
       <c r="F27">
-        <v>232.375</v>
+        <v>241.67</v>
       </c>
       <c r="G27">
         <v>52.4</v>
@@ -3495,28 +3495,28 @@
         <v>56.95</v>
       </c>
       <c r="M27">
-        <v>13.431275</v>
+        <v>13.968526</v>
       </c>
       <c r="N27">
-        <v>43.518725</v>
+        <v>42.981474</v>
       </c>
       <c r="O27">
-        <v>15.23155375</v>
+        <v>15.0435159</v>
       </c>
       <c r="P27">
-        <v>28.28717125</v>
+        <v>27.9379581</v>
       </c>
       <c r="Q27">
-        <v>60.08717125</v>
+        <v>59.7379581</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1798815457696114</v>
+        <v>0.1811722233668013</v>
       </c>
       <c r="T27">
-        <v>0.6587925375292407</v>
+        <v>0.6651341169352977</v>
       </c>
       <c r="U27">
         <v>0.0578</v>
@@ -3533,7 +3533,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>4.2401037876151</v>
+        <v>4.077022872706826</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -3541,22 +3541,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.1438356452914329</v>
+        <v>0.1439818812556574</v>
       </c>
       <c r="C28">
-        <v>813.257079400777</v>
+        <v>802.4688760495852</v>
       </c>
       <c r="D28">
-        <v>1002.527079400777</v>
+        <v>1001.033876049585</v>
       </c>
       <c r="E28">
-        <v>185.17</v>
+        <v>194.465</v>
       </c>
       <c r="F28">
-        <v>241.67</v>
+        <v>250.965</v>
       </c>
       <c r="G28">
         <v>52.4</v>
@@ -3577,45 +3577,45 @@
         <v>56.95</v>
       </c>
       <c r="M28">
-        <v>13.968526</v>
+        <v>15.3841545</v>
       </c>
       <c r="N28">
-        <v>42.981474</v>
+        <v>41.5658455</v>
       </c>
       <c r="O28">
-        <v>15.0435159</v>
+        <v>14.548045925</v>
       </c>
       <c r="P28">
-        <v>27.9379581</v>
+        <v>27.017799575</v>
       </c>
       <c r="Q28">
-        <v>59.7379581</v>
+        <v>58.817799575</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1811722233668013</v>
+        <v>0.1824982619940512</v>
       </c>
       <c r="T28">
-        <v>0.6651341169352977</v>
+        <v>0.6716494382428907</v>
       </c>
       <c r="U28">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V28">
         <v>0.35</v>
       </c>
       <c r="W28">
-        <v>0.03757000000000001</v>
+        <v>0.039845</v>
       </c>
       <c r="X28" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y28">
-        <v>4.077022872706826</v>
+        <v>3.701860898497867</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -3623,22 +3623,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.1439818812556574</v>
+        <v>0.1435366172198818</v>
       </c>
       <c r="C29">
-        <v>802.4688760495852</v>
+        <v>797.7343406561633</v>
       </c>
       <c r="D29">
-        <v>1001.033876049585</v>
+        <v>1005.594340656163</v>
       </c>
       <c r="E29">
-        <v>194.465</v>
+        <v>203.76</v>
       </c>
       <c r="F29">
-        <v>250.965</v>
+        <v>260.26</v>
       </c>
       <c r="G29">
         <v>52.4</v>
@@ -3659,28 +3659,28 @@
         <v>56.95</v>
       </c>
       <c r="M29">
-        <v>15.3841545</v>
+        <v>15.953938</v>
       </c>
       <c r="N29">
-        <v>41.5658455</v>
+        <v>40.996062</v>
       </c>
       <c r="O29">
-        <v>14.548045925</v>
+        <v>14.3486217</v>
       </c>
       <c r="P29">
-        <v>27.017799575</v>
+        <v>26.6474403</v>
       </c>
       <c r="Q29">
-        <v>58.817799575</v>
+        <v>58.4474403</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1824982619940512</v>
+        <v>0.1838611350276136</v>
       </c>
       <c r="T29">
-        <v>0.6716494382428907</v>
+        <v>0.6783457406979166</v>
       </c>
       <c r="U29">
         <v>0.0613</v>
@@ -3697,7 +3697,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>3.701860898497867</v>
+        <v>3.569651580694371</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -3705,22 +3705,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.1435366172198818</v>
+        <v>0.1436191531841062</v>
       </c>
       <c r="C30">
-        <v>797.7343406561633</v>
+        <v>787.5908595987935</v>
       </c>
       <c r="D30">
-        <v>1005.594340656163</v>
+        <v>1004.745859598793</v>
       </c>
       <c r="E30">
-        <v>203.76</v>
+        <v>213.055</v>
       </c>
       <c r="F30">
-        <v>260.26</v>
+        <v>269.555</v>
       </c>
       <c r="G30">
         <v>52.4</v>
@@ -3741,45 +3741,45 @@
         <v>56.95</v>
       </c>
       <c r="M30">
-        <v>15.953938</v>
+        <v>17.2784755</v>
       </c>
       <c r="N30">
-        <v>40.996062</v>
+        <v>39.6715245</v>
       </c>
       <c r="O30">
-        <v>14.3486217</v>
+        <v>13.885033575</v>
       </c>
       <c r="P30">
-        <v>26.6474403</v>
+        <v>25.786490925</v>
       </c>
       <c r="Q30">
-        <v>58.4474403</v>
+        <v>57.586490925</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1838611350276136</v>
+        <v>0.1852623988508538</v>
       </c>
       <c r="T30">
-        <v>0.6783457406979166</v>
+        <v>0.6852306713911125</v>
       </c>
       <c r="U30">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V30">
         <v>0.35</v>
       </c>
       <c r="W30">
-        <v>0.039845</v>
+        <v>0.04166500000000001</v>
       </c>
       <c r="X30" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y30">
-        <v>3.569651580694371</v>
+        <v>3.296008377590951</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -3787,22 +3787,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.1436191531841062</v>
+        <v>0.1431920891483306</v>
       </c>
       <c r="C31">
-        <v>787.5908595987935</v>
+        <v>782.7016673546532</v>
       </c>
       <c r="D31">
-        <v>1004.745859598793</v>
+        <v>1009.151667354653</v>
       </c>
       <c r="E31">
-        <v>213.055</v>
+        <v>222.35</v>
       </c>
       <c r="F31">
-        <v>269.555</v>
+        <v>278.85</v>
       </c>
       <c r="G31">
         <v>52.4</v>
@@ -3823,28 +3823,28 @@
         <v>56.95</v>
       </c>
       <c r="M31">
-        <v>17.2784755</v>
+        <v>17.874285</v>
       </c>
       <c r="N31">
-        <v>39.6715245</v>
+        <v>39.075715</v>
       </c>
       <c r="O31">
-        <v>13.885033575</v>
+        <v>13.67650025</v>
       </c>
       <c r="P31">
-        <v>25.786490925</v>
+        <v>25.39921475</v>
       </c>
       <c r="Q31">
-        <v>57.586490925</v>
+        <v>57.19921475</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1852623988508538</v>
+        <v>0.1867036987833294</v>
       </c>
       <c r="T31">
-        <v>0.6852306713911125</v>
+        <v>0.6923123143898281</v>
       </c>
       <c r="U31">
         <v>0.0641</v>
@@ -3861,7 +3861,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>3.296008377590951</v>
+        <v>3.186141431671253</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -3869,22 +3869,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.1431920891483306</v>
+        <v>0.142765025112555</v>
       </c>
       <c r="C32">
-        <v>782.7016673546532</v>
+        <v>777.8512841973743</v>
       </c>
       <c r="D32">
-        <v>1009.151667354653</v>
+        <v>1013.596284197374</v>
       </c>
       <c r="E32">
-        <v>222.35</v>
+        <v>231.645</v>
       </c>
       <c r="F32">
-        <v>278.85</v>
+        <v>288.145</v>
       </c>
       <c r="G32">
         <v>52.4</v>
@@ -3905,28 +3905,28 @@
         <v>56.95</v>
       </c>
       <c r="M32">
-        <v>17.874285</v>
+        <v>18.4700945</v>
       </c>
       <c r="N32">
-        <v>39.075715</v>
+        <v>38.4799055</v>
       </c>
       <c r="O32">
-        <v>13.67650025</v>
+        <v>13.467966925</v>
       </c>
       <c r="P32">
-        <v>25.39921475</v>
+        <v>25.011938575</v>
       </c>
       <c r="Q32">
-        <v>57.19921475</v>
+        <v>56.811938575</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1867036987833294</v>
+        <v>0.188186775525442</v>
       </c>
       <c r="T32">
-        <v>0.6923123143898281</v>
+        <v>0.6995992224029994</v>
       </c>
       <c r="U32">
         <v>0.0641</v>
@@ -3943,7 +3943,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>3.186141431671253</v>
+        <v>3.08336267581089</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -3951,22 +3951,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.142765025112555</v>
+        <v>0.1439603610767794</v>
       </c>
       <c r="C33">
-        <v>777.8512841973743</v>
+        <v>756.2133376310139</v>
       </c>
       <c r="D33">
-        <v>1013.596284197374</v>
+        <v>1001.253337631014</v>
       </c>
       <c r="E33">
-        <v>231.645</v>
+        <v>240.94</v>
       </c>
       <c r="F33">
-        <v>288.145</v>
+        <v>297.44</v>
       </c>
       <c r="G33">
         <v>52.4</v>
@@ -3987,45 +3987,45 @@
         <v>56.95</v>
       </c>
       <c r="M33">
-        <v>18.4700945</v>
+        <v>21.385936</v>
       </c>
       <c r="N33">
-        <v>38.4799055</v>
+        <v>35.564064</v>
       </c>
       <c r="O33">
-        <v>13.467966925</v>
+        <v>12.4474224</v>
       </c>
       <c r="P33">
-        <v>25.011938575</v>
+        <v>23.1166416</v>
       </c>
       <c r="Q33">
-        <v>56.811938575</v>
+        <v>54.9166416</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.188186775525442</v>
+        <v>0.1897134721717344</v>
       </c>
       <c r="T33">
-        <v>0.6995992224029994</v>
+        <v>0.7071004512400875</v>
       </c>
       <c r="U33">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V33">
         <v>0.35</v>
       </c>
       <c r="W33">
-        <v>0.04166500000000001</v>
+        <v>0.04673500000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y33">
-        <v>3.08336267581089</v>
+        <v>2.662965043942898</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -4033,22 +4033,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.1439603610767794</v>
+        <v>0.1435839970410038</v>
       </c>
       <c r="C34">
-        <v>756.2133376310139</v>
+        <v>750.7720944663635</v>
       </c>
       <c r="D34">
-        <v>1001.253337631014</v>
+        <v>1005.107094466363</v>
       </c>
       <c r="E34">
-        <v>240.94</v>
+        <v>250.235</v>
       </c>
       <c r="F34">
-        <v>297.44</v>
+        <v>306.735</v>
       </c>
       <c r="G34">
         <v>52.4</v>
@@ -4069,28 +4069,28 @@
         <v>56.95</v>
       </c>
       <c r="M34">
-        <v>21.385936</v>
+        <v>22.0542465</v>
       </c>
       <c r="N34">
-        <v>35.564064</v>
+        <v>34.8957535</v>
       </c>
       <c r="O34">
-        <v>12.4474224</v>
+        <v>12.213513725</v>
       </c>
       <c r="P34">
-        <v>23.1166416</v>
+        <v>22.682239775</v>
       </c>
       <c r="Q34">
-        <v>54.9166416</v>
+        <v>54.482239775</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1897134721717344</v>
+        <v>0.1912857418522445</v>
       </c>
       <c r="T34">
-        <v>0.7071004512400875</v>
+        <v>0.7148255973558945</v>
       </c>
       <c r="U34">
         <v>0.07190000000000001</v>
@@ -4107,7 +4107,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>2.662965043942898</v>
+        <v>2.582269133520386</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -4115,22 +4115,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.1435839970410038</v>
+        <v>0.1432076330052282</v>
       </c>
       <c r="C35">
-        <v>750.7720944663635</v>
+        <v>745.3606316265339</v>
       </c>
       <c r="D35">
-        <v>1005.107094466363</v>
+        <v>1008.990631626534</v>
       </c>
       <c r="E35">
-        <v>250.235</v>
+        <v>259.53</v>
       </c>
       <c r="F35">
-        <v>306.735</v>
+        <v>316.03</v>
       </c>
       <c r="G35">
         <v>52.4</v>
@@ -4151,28 +4151,28 @@
         <v>56.95</v>
       </c>
       <c r="M35">
-        <v>22.0542465</v>
+        <v>22.72255700000001</v>
       </c>
       <c r="N35">
-        <v>34.8957535</v>
+        <v>34.22744299999999</v>
       </c>
       <c r="O35">
-        <v>12.213513725</v>
+        <v>11.97960505</v>
       </c>
       <c r="P35">
-        <v>22.682239775</v>
+        <v>22.24783795</v>
       </c>
       <c r="Q35">
-        <v>54.482239775</v>
+        <v>54.04783794999999</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1912857418522445</v>
+        <v>0.1929056560685276</v>
       </c>
       <c r="T35">
-        <v>0.7148255973558945</v>
+        <v>0.7227848388085443</v>
       </c>
       <c r="U35">
         <v>0.07190000000000001</v>
@@ -4189,7 +4189,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>2.582269133520386</v>
+        <v>2.506320041358021</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -4197,22 +4197,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.1432076330052282</v>
+        <v>0.1437185189694526</v>
       </c>
       <c r="C36">
-        <v>745.3606316265339</v>
+        <v>730.8012632807186</v>
       </c>
       <c r="D36">
-        <v>1008.990631626534</v>
+        <v>1003.726263280719</v>
       </c>
       <c r="E36">
-        <v>259.53</v>
+        <v>268.825</v>
       </c>
       <c r="F36">
-        <v>316.03</v>
+        <v>325.325</v>
       </c>
       <c r="G36">
         <v>52.4</v>
@@ -4233,45 +4233,45 @@
         <v>56.95</v>
       </c>
       <c r="M36">
-        <v>22.72255700000001</v>
+        <v>24.65963500000001</v>
       </c>
       <c r="N36">
-        <v>34.22744299999999</v>
+        <v>32.29036499999999</v>
       </c>
       <c r="O36">
-        <v>11.97960505</v>
+        <v>11.30162775</v>
       </c>
       <c r="P36">
-        <v>22.24783795</v>
+        <v>20.98873725</v>
       </c>
       <c r="Q36">
-        <v>54.04783794999999</v>
+        <v>52.78873725</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.1929056560685276</v>
+        <v>0.1945754137991579</v>
       </c>
       <c r="T36">
-        <v>0.7227848388085443</v>
+        <v>0.7309889799981986</v>
       </c>
       <c r="U36">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V36">
         <v>0.35</v>
       </c>
       <c r="W36">
-        <v>0.04673500000000001</v>
+        <v>0.04927000000000001</v>
       </c>
       <c r="X36" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y36">
-        <v>2.506320041358021</v>
+        <v>2.309442130834459</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -4279,22 +4279,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.1437185189694526</v>
+        <v>0.143367504933677</v>
       </c>
       <c r="C37">
-        <v>730.8012632807186</v>
+        <v>725.1173221750462</v>
       </c>
       <c r="D37">
-        <v>1003.726263280719</v>
+        <v>1007.337322175046</v>
       </c>
       <c r="E37">
-        <v>268.825</v>
+        <v>278.1200000000001</v>
       </c>
       <c r="F37">
-        <v>325.325</v>
+        <v>334.6200000000001</v>
       </c>
       <c r="G37">
         <v>52.4</v>
@@ -4315,28 +4315,28 @@
         <v>56.95</v>
       </c>
       <c r="M37">
-        <v>24.65963500000001</v>
+        <v>25.36419600000001</v>
       </c>
       <c r="N37">
-        <v>32.29036499999999</v>
+        <v>31.585804</v>
       </c>
       <c r="O37">
-        <v>11.30162775</v>
+        <v>11.0550314</v>
       </c>
       <c r="P37">
-        <v>20.98873725</v>
+        <v>20.5307726</v>
       </c>
       <c r="Q37">
-        <v>52.78873725</v>
+        <v>52.3307726</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1945754137991579</v>
+        <v>0.1962973514588703</v>
       </c>
       <c r="T37">
-        <v>0.7309889799981986</v>
+        <v>0.7394495006000296</v>
       </c>
       <c r="U37">
         <v>0.07580000000000001</v>
@@ -4353,7 +4353,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>2.309442130834459</v>
+        <v>2.245290960533501</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -4361,22 +4361,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.143367504933677</v>
+        <v>0.1430164908979014</v>
       </c>
       <c r="C38">
-        <v>725.1173221750461</v>
+        <v>719.4594575579247</v>
       </c>
       <c r="D38">
-        <v>1007.337322175046</v>
+        <v>1010.974457557925</v>
       </c>
       <c r="E38">
-        <v>278.12</v>
+        <v>287.415</v>
       </c>
       <c r="F38">
-        <v>334.62</v>
+        <v>343.915</v>
       </c>
       <c r="G38">
         <v>52.4</v>
@@ -4397,28 +4397,28 @@
         <v>56.95</v>
       </c>
       <c r="M38">
-        <v>25.364196</v>
+        <v>26.06875700000001</v>
       </c>
       <c r="N38">
-        <v>31.585804</v>
+        <v>30.881243</v>
       </c>
       <c r="O38">
-        <v>11.0550314</v>
+        <v>10.80843505</v>
       </c>
       <c r="P38">
-        <v>20.5307726</v>
+        <v>20.07280795</v>
       </c>
       <c r="Q38">
-        <v>52.3307726</v>
+        <v>51.87280795</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1962973514588703</v>
+        <v>0.1980739538061927</v>
       </c>
       <c r="T38">
-        <v>0.7394495006000296</v>
+        <v>0.7481786091574741</v>
       </c>
       <c r="U38">
         <v>0.07580000000000001</v>
@@ -4435,7 +4435,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>2.245290960533501</v>
+        <v>2.184607421059623</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -4443,22 +4443,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.1430164908979014</v>
+        <v>0.1426654768621258</v>
       </c>
       <c r="C39">
-        <v>719.4594575579247</v>
+        <v>713.8279529115741</v>
       </c>
       <c r="D39">
-        <v>1010.974457557925</v>
+        <v>1014.637952911574</v>
       </c>
       <c r="E39">
-        <v>287.415</v>
+        <v>296.71</v>
       </c>
       <c r="F39">
-        <v>343.915</v>
+        <v>353.21</v>
       </c>
       <c r="G39">
         <v>52.4</v>
@@ -4479,28 +4479,28 @@
         <v>56.95</v>
       </c>
       <c r="M39">
-        <v>26.06875700000001</v>
+        <v>26.773318</v>
       </c>
       <c r="N39">
-        <v>30.881243</v>
+        <v>30.176682</v>
       </c>
       <c r="O39">
-        <v>10.80843505</v>
+        <v>10.5618387</v>
       </c>
       <c r="P39">
-        <v>20.07280795</v>
+        <v>19.6148433</v>
       </c>
       <c r="Q39">
-        <v>51.87280795</v>
+        <v>51.4148433</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1980739538061927</v>
+        <v>0.1999078659066545</v>
       </c>
       <c r="T39">
-        <v>0.7481786091574741</v>
+        <v>0.7571893018619332</v>
       </c>
       <c r="U39">
         <v>0.07580000000000001</v>
@@ -4517,7 +4517,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>2.184607421059623</v>
+        <v>2.12711775208437</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -4525,22 +4525,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.1426654768621258</v>
+        <v>0.1423144628263502</v>
       </c>
       <c r="C40">
-        <v>713.8279529115741</v>
+        <v>708.223095842208</v>
       </c>
       <c r="D40">
-        <v>1014.637952911574</v>
+        <v>1018.328095842208</v>
       </c>
       <c r="E40">
-        <v>296.71</v>
+        <v>306.005</v>
       </c>
       <c r="F40">
-        <v>353.21</v>
+        <v>362.505</v>
       </c>
       <c r="G40">
         <v>52.4</v>
@@ -4561,28 +4561,28 @@
         <v>56.95</v>
       </c>
       <c r="M40">
-        <v>26.773318</v>
+        <v>27.477879</v>
       </c>
       <c r="N40">
-        <v>30.176682</v>
+        <v>29.472121</v>
       </c>
       <c r="O40">
-        <v>10.5618387</v>
+        <v>10.31524235</v>
       </c>
       <c r="P40">
-        <v>19.6148433</v>
+        <v>19.15687865</v>
       </c>
       <c r="Q40">
-        <v>51.4148433</v>
+        <v>50.95687865</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1999078659066545</v>
+        <v>0.2018019062727053</v>
       </c>
       <c r="T40">
-        <v>0.7571893018619332</v>
+        <v>0.7664954271140795</v>
       </c>
       <c r="U40">
         <v>0.07580000000000001</v>
@@ -4599,7 +4599,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>2.12711775208437</v>
+        <v>2.072576271261694</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -4607,22 +4607,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.1423144628263502</v>
+        <v>0.1419634487905746</v>
       </c>
       <c r="C41">
-        <v>708.223095842208</v>
+        <v>702.6451781552989</v>
       </c>
       <c r="D41">
-        <v>1018.328095842208</v>
+        <v>1022.045178155299</v>
       </c>
       <c r="E41">
-        <v>306.005</v>
+        <v>315.3</v>
       </c>
       <c r="F41">
-        <v>362.505</v>
+        <v>371.8</v>
       </c>
       <c r="G41">
         <v>52.4</v>
@@ -4643,28 +4643,28 @@
         <v>56.95</v>
       </c>
       <c r="M41">
-        <v>27.477879</v>
+        <v>28.18244</v>
       </c>
       <c r="N41">
-        <v>29.472121</v>
+        <v>28.76756</v>
       </c>
       <c r="O41">
-        <v>10.31524235</v>
+        <v>10.068646</v>
       </c>
       <c r="P41">
-        <v>19.15687865</v>
+        <v>18.698914</v>
       </c>
       <c r="Q41">
-        <v>50.95687865</v>
+        <v>50.498914</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.2018019062727053</v>
+        <v>0.2037590813176244</v>
       </c>
       <c r="T41">
-        <v>0.7664954271140795</v>
+        <v>0.7761117565412972</v>
       </c>
       <c r="U41">
         <v>0.07580000000000001</v>
@@ -4681,7 +4681,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>2.072576271261694</v>
+        <v>2.020761864480151</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -4689,22 +4689,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.1419634487905746</v>
+        <v>0.145396734754799</v>
       </c>
       <c r="C42">
-        <v>702.6451781552989</v>
+        <v>658.1183668554336</v>
       </c>
       <c r="D42">
-        <v>1022.045178155299</v>
+        <v>986.8133668554336</v>
       </c>
       <c r="E42">
-        <v>315.3</v>
+        <v>324.595</v>
       </c>
       <c r="F42">
-        <v>371.8</v>
+        <v>381.095</v>
       </c>
       <c r="G42">
         <v>52.4</v>
@@ -4725,45 +4725,45 @@
         <v>56.95</v>
       </c>
       <c r="M42">
-        <v>28.18244</v>
+        <v>34.29855</v>
       </c>
       <c r="N42">
-        <v>28.76756</v>
+        <v>22.65145</v>
       </c>
       <c r="O42">
-        <v>10.068646</v>
+        <v>7.928007500000001</v>
       </c>
       <c r="P42">
-        <v>18.698914</v>
+        <v>14.7234425</v>
       </c>
       <c r="Q42">
-        <v>50.498914</v>
+        <v>46.5234425</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.2037590813176244</v>
+        <v>0.2057826012793204</v>
       </c>
       <c r="T42">
-        <v>0.7761117565412972</v>
+        <v>0.7860540632372341</v>
       </c>
       <c r="U42">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V42">
         <v>0.35</v>
       </c>
       <c r="W42">
-        <v>0.04927000000000001</v>
+        <v>0.0585</v>
       </c>
       <c r="X42" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y42">
-        <v>2.020761864480151</v>
+        <v>1.660420046911604</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -4771,22 +4771,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.145396734754799</v>
+        <v>0.1451380207190234</v>
       </c>
       <c r="C43">
-        <v>658.1183668554336</v>
+        <v>651.3934046601789</v>
       </c>
       <c r="D43">
-        <v>986.8133668554336</v>
+        <v>989.3834046601789</v>
       </c>
       <c r="E43">
-        <v>324.595</v>
+        <v>333.89</v>
       </c>
       <c r="F43">
-        <v>381.095</v>
+        <v>390.39</v>
       </c>
       <c r="G43">
         <v>52.4</v>
@@ -4807,28 +4807,28 @@
         <v>56.95</v>
       </c>
       <c r="M43">
-        <v>34.29855</v>
+        <v>35.1351</v>
       </c>
       <c r="N43">
-        <v>22.65145</v>
+        <v>21.8149</v>
       </c>
       <c r="O43">
-        <v>7.928007500000001</v>
+        <v>7.635215</v>
       </c>
       <c r="P43">
-        <v>14.7234425</v>
+        <v>14.179685</v>
       </c>
       <c r="Q43">
-        <v>46.5234425</v>
+        <v>45.979685</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.2057826012793204</v>
+        <v>0.2078758977914197</v>
       </c>
       <c r="T43">
-        <v>0.7860540632372341</v>
+        <v>0.7963392080950999</v>
       </c>
       <c r="U43">
         <v>0.09</v>
@@ -4845,7 +4845,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>1.660420046911604</v>
+        <v>1.620886236270852</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -4853,22 +4853,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.1451380207190235</v>
+        <v>0.1448793066832479</v>
       </c>
       <c r="C44">
-        <v>651.3934046601788</v>
+        <v>644.6818641343893</v>
       </c>
       <c r="D44">
-        <v>989.3834046601787</v>
+        <v>991.9668641343892</v>
       </c>
       <c r="E44">
-        <v>333.89</v>
+        <v>343.185</v>
       </c>
       <c r="F44">
-        <v>390.39</v>
+        <v>399.685</v>
       </c>
       <c r="G44">
         <v>52.4</v>
@@ -4889,28 +4889,28 @@
         <v>56.95</v>
       </c>
       <c r="M44">
-        <v>35.13509999999999</v>
+        <v>35.97165</v>
       </c>
       <c r="N44">
-        <v>21.81490000000001</v>
+        <v>20.97835000000001</v>
       </c>
       <c r="O44">
-        <v>7.635215000000002</v>
+        <v>7.342422500000001</v>
       </c>
       <c r="P44">
-        <v>14.17968500000001</v>
+        <v>13.6359275</v>
       </c>
       <c r="Q44">
-        <v>45.979685</v>
+        <v>45.43592750000001</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.2078758977914197</v>
+        <v>0.2100426433039436</v>
       </c>
       <c r="T44">
-        <v>0.7963392080950999</v>
+        <v>0.8069852352286805</v>
       </c>
       <c r="U44">
         <v>0.09</v>
@@ -4927,7 +4927,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>1.620886236270852</v>
+        <v>1.583191207520367</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -4935,22 +4935,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.1448793066832479</v>
+        <v>0.1446205926474723</v>
       </c>
       <c r="C45">
-        <v>644.6818641343893</v>
+        <v>637.9838506925589</v>
       </c>
       <c r="D45">
-        <v>991.9668641343892</v>
+        <v>994.563850692559</v>
       </c>
       <c r="E45">
-        <v>343.185</v>
+        <v>352.48</v>
       </c>
       <c r="F45">
-        <v>399.685</v>
+        <v>408.98</v>
       </c>
       <c r="G45">
         <v>52.4</v>
@@ -4971,28 +4971,28 @@
         <v>56.95</v>
       </c>
       <c r="M45">
-        <v>35.97165</v>
+        <v>36.8082</v>
       </c>
       <c r="N45">
-        <v>20.97835000000001</v>
+        <v>20.1418</v>
       </c>
       <c r="O45">
-        <v>7.342422500000001</v>
+        <v>7.049630000000001</v>
       </c>
       <c r="P45">
-        <v>13.6359275</v>
+        <v>13.09217</v>
       </c>
       <c r="Q45">
-        <v>45.43592750000001</v>
+        <v>44.89217</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.2100426433039436</v>
+        <v>0.2122867725847719</v>
       </c>
       <c r="T45">
-        <v>0.8069852352286805</v>
+        <v>0.8180114776170316</v>
       </c>
       <c r="U45">
         <v>0.09</v>
@@ -5009,7 +5009,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>1.583191207520367</v>
+        <v>1.547209589167631</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -5017,22 +5017,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.1446205926474723</v>
+        <v>0.1443618786116967</v>
       </c>
       <c r="C46">
-        <v>637.9838506925589</v>
+        <v>631.2994708559886</v>
       </c>
       <c r="D46">
-        <v>994.563850692559</v>
+        <v>997.1744708559886</v>
       </c>
       <c r="E46">
-        <v>352.48</v>
+        <v>361.775</v>
       </c>
       <c r="F46">
-        <v>408.98</v>
+        <v>418.275</v>
       </c>
       <c r="G46">
         <v>52.4</v>
@@ -5053,28 +5053,28 @@
         <v>56.95</v>
       </c>
       <c r="M46">
-        <v>36.8082</v>
+        <v>37.64475</v>
       </c>
       <c r="N46">
-        <v>20.1418</v>
+        <v>19.30525</v>
       </c>
       <c r="O46">
-        <v>7.049630000000001</v>
+        <v>6.7568375</v>
       </c>
       <c r="P46">
-        <v>13.09217</v>
+        <v>12.5484125</v>
       </c>
       <c r="Q46">
-        <v>44.89217</v>
+        <v>44.34841249999999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.2122867725847719</v>
+        <v>0.2146125065667212</v>
       </c>
       <c r="T46">
-        <v>0.8180114776170316</v>
+        <v>0.82943867427405</v>
       </c>
       <c r="U46">
         <v>0.09</v>
@@ -5091,7 +5091,7 @@
         </is>
       </c>
       <c r="Y46">
-        <v>1.547209589167631</v>
+        <v>1.512827153852795</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -5099,22 +5099,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.1443618786116967</v>
+        <v>0.1649212479783982</v>
       </c>
       <c r="C47">
-        <v>631.2994708559886</v>
+        <v>449.9001769764347</v>
       </c>
       <c r="D47">
-        <v>997.1744708559886</v>
+        <v>825.0701769764347</v>
       </c>
       <c r="E47">
-        <v>361.775</v>
+        <v>371.07</v>
       </c>
       <c r="F47">
-        <v>418.275</v>
+        <v>427.57</v>
       </c>
       <c r="G47">
         <v>52.4</v>
@@ -5135,45 +5135,45 @@
         <v>56.95</v>
       </c>
       <c r="M47">
-        <v>37.64475</v>
+        <v>62.767276</v>
       </c>
       <c r="N47">
-        <v>19.30525</v>
+        <v>-5.817276</v>
       </c>
       <c r="O47">
-        <v>6.7568375</v>
+        <v>-2.0360466</v>
       </c>
       <c r="P47">
-        <v>12.5484125</v>
+        <v>-3.7812294</v>
       </c>
       <c r="Q47">
-        <v>44.34841249999999</v>
+        <v>28.0187706</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.2146125065667212</v>
+        <v>0.2200695794152993</v>
       </c>
       <c r="T47">
-        <v>0.82943867427405</v>
+        <v>0.8562513042207095</v>
       </c>
       <c r="U47">
-        <v>0.09</v>
+        <v>0.1468</v>
       </c>
       <c r="V47">
-        <v>0.35</v>
+        <v>0.3175619728981069</v>
       </c>
       <c r="W47">
-        <v>0.0585</v>
+        <v>0.1001819023785579</v>
       </c>
       <c r="X47" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Ca2/CC</t>
         </is>
       </c>
       <c r="Y47">
-        <v>1.512827153852795</v>
+        <v>0.9073199225660199</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -5181,22 +5181,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.1649212479783982</v>
+        <v>0.1659312479783982</v>
       </c>
       <c r="C48">
-        <v>449.9001769764347</v>
+        <v>433.6684232777131</v>
       </c>
       <c r="D48">
-        <v>825.0701769764347</v>
+        <v>818.1334232777132</v>
       </c>
       <c r="E48">
-        <v>371.07</v>
+        <v>380.365</v>
       </c>
       <c r="F48">
-        <v>427.57</v>
+        <v>436.865</v>
       </c>
       <c r="G48">
         <v>52.4</v>
@@ -5217,37 +5217,37 @@
         <v>56.95</v>
       </c>
       <c r="M48">
-        <v>62.767276</v>
+        <v>64.131782</v>
       </c>
       <c r="N48">
-        <v>-5.817276</v>
+        <v>-7.181781999999998</v>
       </c>
       <c r="O48">
-        <v>-2.0360466</v>
+        <v>-2.513623699999999</v>
       </c>
       <c r="P48">
-        <v>-3.7812294</v>
+        <v>-4.668158299999999</v>
       </c>
       <c r="Q48">
-        <v>28.0187706</v>
+        <v>27.1318417</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.2200695794152993</v>
+        <v>0.223357684687286</v>
       </c>
       <c r="T48">
-        <v>0.8562513042207095</v>
+        <v>0.8724069892060058</v>
       </c>
       <c r="U48">
         <v>0.1468</v>
       </c>
       <c r="V48">
-        <v>0.3175619728981069</v>
+        <v>0.3108053351768706</v>
       </c>
       <c r="W48">
-        <v>0.1001819023785579</v>
+        <v>0.1011737767960354</v>
       </c>
       <c r="X48" t="inlineStr">
         <is>
@@ -5255,7 +5255,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>0.9073199225660199</v>
+        <v>0.8880152433624876</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -5263,22 +5263,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.1659312479783982</v>
+        <v>0.1669412479783982</v>
       </c>
       <c r="C49">
-        <v>433.6684232777131</v>
+        <v>417.5523382113132</v>
       </c>
       <c r="D49">
-        <v>818.1334232777132</v>
+        <v>811.3123382113132</v>
       </c>
       <c r="E49">
-        <v>380.365</v>
+        <v>389.66</v>
       </c>
       <c r="F49">
-        <v>436.865</v>
+        <v>446.16</v>
       </c>
       <c r="G49">
         <v>52.4</v>
@@ -5299,37 +5299,37 @@
         <v>56.95</v>
       </c>
       <c r="M49">
-        <v>64.131782</v>
+        <v>65.49628800000001</v>
       </c>
       <c r="N49">
-        <v>-7.181781999999998</v>
+        <v>-8.546288000000004</v>
       </c>
       <c r="O49">
-        <v>-2.513623699999999</v>
+        <v>-2.991200800000001</v>
       </c>
       <c r="P49">
-        <v>-4.668158299999999</v>
+        <v>-5.555087200000003</v>
       </c>
       <c r="Q49">
-        <v>27.1318417</v>
+        <v>26.24491279999999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.223357684687286</v>
+        <v>0.2267722555466569</v>
       </c>
       <c r="T49">
-        <v>0.8724069892060058</v>
+        <v>0.8891840466907368</v>
       </c>
       <c r="U49">
         <v>0.1468</v>
       </c>
       <c r="V49">
-        <v>0.3108053351768706</v>
+        <v>0.3043302240273525</v>
       </c>
       <c r="W49">
-        <v>0.1011737767960354</v>
+        <v>0.1021243231127847</v>
       </c>
       <c r="X49" t="inlineStr">
         <is>
@@ -5337,7 +5337,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>0.8880152433624876</v>
+        <v>0.8695149257924357</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -5345,22 +5345,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.1669412479783982</v>
+        <v>0.1679512479783982</v>
       </c>
       <c r="C50">
-        <v>417.5523382113132</v>
+        <v>401.549052580549</v>
       </c>
       <c r="D50">
-        <v>811.3123382113132</v>
+        <v>804.604052580549</v>
       </c>
       <c r="E50">
-        <v>389.66</v>
+        <v>398.955</v>
       </c>
       <c r="F50">
-        <v>446.16</v>
+        <v>455.455</v>
       </c>
       <c r="G50">
         <v>52.4</v>
@@ -5381,37 +5381,37 @@
         <v>56.95</v>
       </c>
       <c r="M50">
-        <v>65.49628800000001</v>
+        <v>66.860794</v>
       </c>
       <c r="N50">
-        <v>-8.546288000000004</v>
+        <v>-9.910793999999996</v>
       </c>
       <c r="O50">
-        <v>-2.991200800000001</v>
+        <v>-3.468777899999998</v>
       </c>
       <c r="P50">
-        <v>-5.555087200000003</v>
+        <v>-6.442016099999997</v>
       </c>
       <c r="Q50">
-        <v>26.24491279999999</v>
+        <v>25.3579839</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.2267722555466569</v>
+        <v>0.230320731145611</v>
       </c>
       <c r="T50">
-        <v>0.8891840466907368</v>
+        <v>0.9066190279983982</v>
       </c>
       <c r="U50">
         <v>0.1468</v>
       </c>
       <c r="V50">
-        <v>0.3043302240273525</v>
+        <v>0.2981194031288351</v>
       </c>
       <c r="W50">
-        <v>0.1021243231127847</v>
+        <v>0.103036071620687</v>
       </c>
       <c r="X50" t="inlineStr">
         <is>
@@ -5419,7 +5419,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>0.8695149257924357</v>
+        <v>0.8517697232252432</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -5427,22 +5427,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.1679512479783982</v>
+        <v>0.1689612479783982</v>
       </c>
       <c r="C51">
-        <v>401.549052580549</v>
+        <v>385.6557913056315</v>
       </c>
       <c r="D51">
-        <v>804.604052580549</v>
+        <v>798.0057913056315</v>
       </c>
       <c r="E51">
-        <v>398.955</v>
+        <v>408.25</v>
       </c>
       <c r="F51">
-        <v>455.455</v>
+        <v>464.75</v>
       </c>
       <c r="G51">
         <v>52.4</v>
@@ -5463,37 +5463,37 @@
         <v>56.95</v>
       </c>
       <c r="M51">
-        <v>66.860794</v>
+        <v>68.2253</v>
       </c>
       <c r="N51">
-        <v>-9.910793999999996</v>
+        <v>-11.2753</v>
       </c>
       <c r="O51">
-        <v>-3.468777899999998</v>
+        <v>-3.946355</v>
       </c>
       <c r="P51">
-        <v>-6.442016099999997</v>
+        <v>-7.328945000000001</v>
       </c>
       <c r="Q51">
-        <v>25.3579839</v>
+        <v>24.471055</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.230320731145611</v>
+        <v>0.2340111457685232</v>
       </c>
       <c r="T51">
-        <v>0.9066190279983982</v>
+        <v>0.9247514085583662</v>
       </c>
       <c r="U51">
         <v>0.1468</v>
       </c>
       <c r="V51">
-        <v>0.2981194031288351</v>
+        <v>0.2921570150662584</v>
       </c>
       <c r="W51">
-        <v>0.103036071620687</v>
+        <v>0.1039113501882733</v>
       </c>
       <c r="X51" t="inlineStr">
         <is>
@@ -5501,7 +5501,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>0.8517697232252432</v>
+        <v>0.8347343287607383</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -5509,22 +5509,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.1689612479783982</v>
+        <v>0.1699712479783982</v>
       </c>
       <c r="C52">
-        <v>385.6557913056315</v>
+        <v>369.8698695959704</v>
       </c>
       <c r="D52">
-        <v>798.0057913056315</v>
+        <v>791.5148695959705</v>
       </c>
       <c r="E52">
-        <v>408.25</v>
+        <v>417.545</v>
       </c>
       <c r="F52">
-        <v>464.75</v>
+        <v>474.045</v>
       </c>
       <c r="G52">
         <v>52.4</v>
@@ -5545,37 +5545,37 @@
         <v>56.95</v>
       </c>
       <c r="M52">
-        <v>68.2253</v>
+        <v>69.58980600000001</v>
       </c>
       <c r="N52">
-        <v>-11.2753</v>
+        <v>-12.63980600000001</v>
       </c>
       <c r="O52">
-        <v>-3.946355</v>
+        <v>-4.423932100000002</v>
       </c>
       <c r="P52">
-        <v>-7.328945000000001</v>
+        <v>-8.215873900000005</v>
       </c>
       <c r="Q52">
-        <v>24.471055</v>
+        <v>23.58412609999999</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.2340111457685232</v>
+        <v>0.2378521895597176</v>
       </c>
       <c r="T52">
-        <v>0.9247514085583662</v>
+        <v>0.9436238862840473</v>
       </c>
       <c r="U52">
         <v>0.1468</v>
       </c>
       <c r="V52">
-        <v>0.2921570150662584</v>
+        <v>0.2864284461433906</v>
       </c>
       <c r="W52">
-        <v>0.1039113501882733</v>
+        <v>0.1047523041061503</v>
       </c>
       <c r="X52" t="inlineStr">
         <is>
@@ -5583,7 +5583,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>0.8347343287607383</v>
+        <v>0.8183669889811159</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -5591,22 +5591,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.1699712479783982</v>
+        <v>0.1709812479783983</v>
       </c>
       <c r="C53">
-        <v>369.8698695959704</v>
+        <v>354.1886893077703</v>
       </c>
       <c r="D53">
-        <v>791.5148695959705</v>
+        <v>785.1286893077704</v>
       </c>
       <c r="E53">
-        <v>417.545</v>
+        <v>426.84</v>
       </c>
       <c r="F53">
-        <v>474.045</v>
+        <v>483.34</v>
       </c>
       <c r="G53">
         <v>52.4</v>
@@ -5627,37 +5627,37 @@
         <v>56.95</v>
       </c>
       <c r="M53">
-        <v>69.58980600000001</v>
+        <v>70.95431200000002</v>
       </c>
       <c r="N53">
-        <v>-12.63980600000001</v>
+        <v>-14.00431200000001</v>
       </c>
       <c r="O53">
-        <v>-4.423932100000002</v>
+        <v>-4.901509200000004</v>
       </c>
       <c r="P53">
-        <v>-8.215873900000005</v>
+        <v>-9.10280280000001</v>
       </c>
       <c r="Q53">
-        <v>23.58412609999999</v>
+        <v>22.69719719999999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.2378521895597176</v>
+        <v>0.2418532768422117</v>
       </c>
       <c r="T53">
-        <v>0.9436238862840473</v>
+        <v>0.9632827172482983</v>
       </c>
       <c r="U53">
         <v>0.1468</v>
       </c>
       <c r="V53">
-        <v>0.2864284461433906</v>
+        <v>0.2809202067944792</v>
       </c>
       <c r="W53">
-        <v>0.1047523041061503</v>
+        <v>0.1055609136425705</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
@@ -5665,7 +5665,7 @@
         </is>
       </c>
       <c r="Y53">
-        <v>0.8183669889811159</v>
+        <v>0.8026291622699405</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -5673,22 +5673,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.1709812479783983</v>
+        <v>0.2049405090153315</v>
       </c>
       <c r="C54">
-        <v>354.1886893077703</v>
+        <v>177.3537570004082</v>
       </c>
       <c r="D54">
-        <v>785.1286893077704</v>
+        <v>617.5887570004082</v>
       </c>
       <c r="E54">
-        <v>426.84</v>
+        <v>436.135</v>
       </c>
       <c r="F54">
-        <v>483.34</v>
+        <v>492.635</v>
       </c>
       <c r="G54">
         <v>52.4</v>
@@ -5709,45 +5709,45 @@
         <v>56.95</v>
       </c>
       <c r="M54">
-        <v>70.95431200000002</v>
+        <v>98.92110800000002</v>
       </c>
       <c r="N54">
-        <v>-14.00431200000001</v>
+        <v>-41.97110800000002</v>
       </c>
       <c r="O54">
-        <v>-4.901509200000004</v>
+        <v>-14.6898878</v>
       </c>
       <c r="P54">
-        <v>-9.10280280000001</v>
+        <v>-27.28122020000001</v>
       </c>
       <c r="Q54">
-        <v>22.69719719999999</v>
+        <v>4.518779799999987</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.2418532768422117</v>
+        <v>0.255235816853606</v>
       </c>
       <c r="T54">
-        <v>0.9632827172482983</v>
+        <v>1.029036117107231</v>
       </c>
       <c r="U54">
-        <v>0.1468</v>
+        <v>0.2008</v>
       </c>
       <c r="V54">
-        <v>0.2809202067944792</v>
+        <v>0.2014989561176367</v>
       </c>
       <c r="W54">
-        <v>0.1055609136425705</v>
+        <v>0.1603390096115786</v>
       </c>
       <c r="X54" t="inlineStr">
         <is>
-          <t>Ca2/CC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y54">
-        <v>0.8026291622699405</v>
+        <v>0.5757113031932476</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -5755,22 +5755,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.2049405090153315</v>
+        <v>0.2064905090153314</v>
       </c>
       <c r="C55">
-        <v>177.3537570004082</v>
+        <v>162.1015752152707</v>
       </c>
       <c r="D55">
-        <v>617.5887570004082</v>
+        <v>611.6315752152707</v>
       </c>
       <c r="E55">
-        <v>436.135</v>
+        <v>445.43</v>
       </c>
       <c r="F55">
-        <v>492.635</v>
+        <v>501.93</v>
       </c>
       <c r="G55">
         <v>52.4</v>
@@ -5791,37 +5791,37 @@
         <v>56.95</v>
       </c>
       <c r="M55">
-        <v>98.92110800000002</v>
+        <v>100.787544</v>
       </c>
       <c r="N55">
-        <v>-41.97110800000002</v>
+        <v>-43.83754400000001</v>
       </c>
       <c r="O55">
-        <v>-14.6898878</v>
+        <v>-15.3431404</v>
       </c>
       <c r="P55">
-        <v>-27.28122020000001</v>
+        <v>-28.49440360000001</v>
       </c>
       <c r="Q55">
-        <v>4.518779799999987</v>
+        <v>3.305596399999992</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.255235816853606</v>
+        <v>0.2597887693939017</v>
       </c>
       <c r="T55">
-        <v>1.029036117107231</v>
+        <v>1.051406467479127</v>
       </c>
       <c r="U55">
         <v>0.2008</v>
       </c>
       <c r="V55">
-        <v>0.2014989561176367</v>
+        <v>0.1977674939673101</v>
       </c>
       <c r="W55">
-        <v>0.1603390096115786</v>
+        <v>0.1610882872113641</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
@@ -5829,7 +5829,7 @@
         </is>
       </c>
       <c r="Y55">
-        <v>0.5757113031932476</v>
+        <v>0.5650499827637431</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -5837,22 +5837,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.2064905090153314</v>
+        <v>0.2080405090153315</v>
       </c>
       <c r="C56">
-        <v>162.1015752152707</v>
+        <v>146.9632198945959</v>
       </c>
       <c r="D56">
-        <v>611.6315752152707</v>
+        <v>605.788219894596</v>
       </c>
       <c r="E56">
-        <v>445.43</v>
+        <v>454.725</v>
       </c>
       <c r="F56">
-        <v>501.93</v>
+        <v>511.225</v>
       </c>
       <c r="G56">
         <v>52.4</v>
@@ -5873,37 +5873,37 @@
         <v>56.95</v>
       </c>
       <c r="M56">
-        <v>100.787544</v>
+        <v>102.65398</v>
       </c>
       <c r="N56">
-        <v>-43.83754400000001</v>
+        <v>-45.70398</v>
       </c>
       <c r="O56">
-        <v>-15.3431404</v>
+        <v>-15.996393</v>
       </c>
       <c r="P56">
-        <v>-28.49440360000001</v>
+        <v>-29.707587</v>
       </c>
       <c r="Q56">
-        <v>3.305596399999992</v>
+        <v>2.092412999999993</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.2597887693939017</v>
+        <v>0.264544075380433</v>
       </c>
       <c r="T56">
-        <v>1.051406467479127</v>
+        <v>1.07477105564533</v>
       </c>
       <c r="U56">
         <v>0.2008</v>
       </c>
       <c r="V56">
-        <v>0.1977674939673101</v>
+        <v>0.1941717213497226</v>
       </c>
       <c r="W56">
-        <v>0.1610882872113641</v>
+        <v>0.1618103183529757</v>
       </c>
       <c r="X56" t="inlineStr">
         <is>
@@ -5911,7 +5911,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>0.5650499827637431</v>
+        <v>0.5547763467134932</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -5919,22 +5919,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.2080405090153315</v>
+        <v>0.2095905090153314</v>
       </c>
       <c r="C57">
-        <v>146.9632198945959</v>
+        <v>131.935459513781</v>
       </c>
       <c r="D57">
-        <v>605.788219894596</v>
+        <v>600.0554595137811</v>
       </c>
       <c r="E57">
-        <v>454.725</v>
+        <v>464.0200000000001</v>
       </c>
       <c r="F57">
-        <v>511.225</v>
+        <v>520.5200000000001</v>
       </c>
       <c r="G57">
         <v>52.4</v>
@@ -5955,37 +5955,37 @@
         <v>56.95</v>
       </c>
       <c r="M57">
-        <v>102.65398</v>
+        <v>104.520416</v>
       </c>
       <c r="N57">
-        <v>-45.70398</v>
+        <v>-47.57041600000002</v>
       </c>
       <c r="O57">
-        <v>-15.996393</v>
+        <v>-16.64964560000001</v>
       </c>
       <c r="P57">
-        <v>-29.707587</v>
+        <v>-30.92077040000002</v>
       </c>
       <c r="Q57">
-        <v>2.092412999999993</v>
+        <v>0.8792295999999808</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.264544075380433</v>
+        <v>0.2695155316390791</v>
       </c>
       <c r="T57">
-        <v>1.07477105564533</v>
+        <v>1.09919767054636</v>
       </c>
       <c r="U57">
         <v>0.2008</v>
       </c>
       <c r="V57">
-        <v>0.1941717213497226</v>
+        <v>0.1907043691827633</v>
       </c>
       <c r="W57">
-        <v>0.1618103183529757</v>
+        <v>0.1625065626681012</v>
       </c>
       <c r="X57" t="inlineStr">
         <is>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>0.5547763467134932</v>
+        <v>0.5448696262364665</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -6001,22 +6001,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.2095905090153314</v>
+        <v>0.2111405090153314</v>
       </c>
       <c r="C58">
-        <v>131.935459513781</v>
+        <v>117.0151837251349</v>
       </c>
       <c r="D58">
-        <v>600.0554595137811</v>
+        <v>594.430183725135</v>
       </c>
       <c r="E58">
-        <v>464.0200000000001</v>
+        <v>473.3150000000001</v>
       </c>
       <c r="F58">
-        <v>520.5200000000001</v>
+        <v>529.8150000000001</v>
       </c>
       <c r="G58">
         <v>52.4</v>
@@ -6037,37 +6037,37 @@
         <v>56.95</v>
       </c>
       <c r="M58">
-        <v>104.520416</v>
+        <v>106.386852</v>
       </c>
       <c r="N58">
-        <v>-47.57041600000002</v>
+        <v>-49.43685200000002</v>
       </c>
       <c r="O58">
-        <v>-16.64964560000001</v>
+        <v>-17.3028982</v>
       </c>
       <c r="P58">
-        <v>-30.92077040000002</v>
+        <v>-32.13395380000001</v>
       </c>
       <c r="Q58">
-        <v>0.8792295999999808</v>
+        <v>-0.3339538000000175</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.2695155316390791</v>
+        <v>0.2747182184213833</v>
       </c>
       <c r="T58">
-        <v>1.09919767054636</v>
+        <v>1.124760407070694</v>
       </c>
       <c r="U58">
         <v>0.2008</v>
       </c>
       <c r="V58">
-        <v>0.1907043691827633</v>
+        <v>0.1873586784953464</v>
       </c>
       <c r="W58">
-        <v>0.1625065626681012</v>
+        <v>0.1631783773581345</v>
       </c>
       <c r="X58" t="inlineStr">
         <is>
@@ -6075,7 +6075,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>0.5448696262364665</v>
+        <v>0.5353105099867039</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -6083,22 +6083,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.2111405090153314</v>
+        <v>0.2126905090153314</v>
       </c>
       <c r="C59">
-        <v>117.0151837251349</v>
+        <v>102.199397730712</v>
       </c>
       <c r="D59">
-        <v>594.430183725135</v>
+        <v>588.909397730712</v>
       </c>
       <c r="E59">
-        <v>473.3150000000001</v>
+        <v>482.61</v>
       </c>
       <c r="F59">
-        <v>529.8150000000001</v>
+        <v>539.11</v>
       </c>
       <c r="G59">
         <v>52.4</v>
@@ -6119,37 +6119,37 @@
         <v>56.95</v>
       </c>
       <c r="M59">
-        <v>106.386852</v>
+        <v>108.253288</v>
       </c>
       <c r="N59">
-        <v>-49.43685200000002</v>
+        <v>-51.30328800000001</v>
       </c>
       <c r="O59">
-        <v>-17.3028982</v>
+        <v>-17.9561508</v>
       </c>
       <c r="P59">
-        <v>-32.13395380000001</v>
+        <v>-33.34713720000001</v>
       </c>
       <c r="Q59">
-        <v>-0.3339538000000175</v>
+        <v>-1.547137200000009</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.2747182184213833</v>
+        <v>0.280168652193321</v>
       </c>
       <c r="T59">
-        <v>1.124760407070694</v>
+        <v>1.151540416762854</v>
       </c>
       <c r="U59">
         <v>0.2008</v>
       </c>
       <c r="V59">
-        <v>0.1873586784953464</v>
+        <v>0.1841283564523231</v>
       </c>
       <c r="W59">
-        <v>0.1631783773581345</v>
+        <v>0.1638270260243735</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
@@ -6157,7 +6157,7 @@
         </is>
       </c>
       <c r="Y59">
-        <v>0.5353105099867039</v>
+        <v>0.526081018435209</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -6165,22 +6165,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.2126905090153314</v>
+        <v>0.2142405090153314</v>
       </c>
       <c r="C60">
-        <v>102.1993977307121</v>
+        <v>87.48521696583134</v>
       </c>
       <c r="D60">
-        <v>588.9093977307122</v>
+        <v>583.4902169658313</v>
       </c>
       <c r="E60">
-        <v>482.61</v>
+        <v>491.905</v>
       </c>
       <c r="F60">
-        <v>539.11</v>
+        <v>548.405</v>
       </c>
       <c r="G60">
         <v>52.4</v>
@@ -6201,37 +6201,37 @@
         <v>56.95</v>
       </c>
       <c r="M60">
-        <v>108.253288</v>
+        <v>110.119724</v>
       </c>
       <c r="N60">
-        <v>-51.30328800000001</v>
+        <v>-53.169724</v>
       </c>
       <c r="O60">
-        <v>-17.9561508</v>
+        <v>-18.6094034</v>
       </c>
       <c r="P60">
-        <v>-33.34713720000001</v>
+        <v>-34.5603206</v>
       </c>
       <c r="Q60">
-        <v>-1.547137200000009</v>
+        <v>-2.760320600000007</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.2801686521933209</v>
+        <v>0.2858849607834019</v>
       </c>
       <c r="T60">
-        <v>1.151540416762853</v>
+        <v>1.179626768391216</v>
       </c>
       <c r="U60">
         <v>0.2008</v>
       </c>
       <c r="V60">
-        <v>0.1841283564523231</v>
+        <v>0.1810075368514363</v>
       </c>
       <c r="W60">
-        <v>0.1638270260243735</v>
+        <v>0.1644536866002316</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
@@ -6239,7 +6239,7 @@
         </is>
       </c>
       <c r="Y60">
-        <v>0.526081018435209</v>
+        <v>0.5171643910041039</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -6247,22 +6247,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.2142405090153314</v>
+        <v>0.2157905090153315</v>
       </c>
       <c r="C61">
-        <v>87.48521696583134</v>
+        <v>72.86986207345626</v>
       </c>
       <c r="D61">
-        <v>583.4902169658313</v>
+        <v>578.1698620734562</v>
       </c>
       <c r="E61">
-        <v>491.905</v>
+        <v>501.1999999999999</v>
       </c>
       <c r="F61">
-        <v>548.405</v>
+        <v>557.6999999999999</v>
       </c>
       <c r="G61">
         <v>52.4</v>
@@ -6283,37 +6283,37 @@
         <v>56.95</v>
       </c>
       <c r="M61">
-        <v>110.119724</v>
+        <v>111.98616</v>
       </c>
       <c r="N61">
-        <v>-53.169724</v>
+        <v>-55.03615999999998</v>
       </c>
       <c r="O61">
-        <v>-18.6094034</v>
+        <v>-19.26265599999999</v>
       </c>
       <c r="P61">
-        <v>-34.5603206</v>
+        <v>-35.77350399999999</v>
       </c>
       <c r="Q61">
-        <v>-2.760320600000007</v>
+        <v>-3.973503999999991</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.2858849607834019</v>
+        <v>0.291887084802987</v>
       </c>
       <c r="T61">
-        <v>1.179626768391216</v>
+        <v>1.209117437600996</v>
       </c>
       <c r="U61">
         <v>0.2008</v>
       </c>
       <c r="V61">
-        <v>0.1810075368514363</v>
+        <v>0.1779907445705791</v>
       </c>
       <c r="W61">
-        <v>0.1644536866002316</v>
+        <v>0.1650594584902277</v>
       </c>
       <c r="X61" t="inlineStr">
         <is>
@@ -6321,7 +6321,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>0.5171643910041039</v>
+        <v>0.5085449844873688</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -6329,22 +6329,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.2157905090153315</v>
+        <v>0.2173405090153314</v>
       </c>
       <c r="C62">
-        <v>72.86986207345626</v>
+        <v>58.35065415103622</v>
       </c>
       <c r="D62">
-        <v>578.1698620734562</v>
+        <v>572.9456541510363</v>
       </c>
       <c r="E62">
-        <v>501.1999999999999</v>
+        <v>510.495</v>
       </c>
       <c r="F62">
-        <v>557.6999999999999</v>
+        <v>566.995</v>
       </c>
       <c r="G62">
         <v>52.4</v>
@@ -6365,37 +6365,37 @@
         <v>56.95</v>
       </c>
       <c r="M62">
-        <v>111.98616</v>
+        <v>113.852596</v>
       </c>
       <c r="N62">
-        <v>-55.03615999999998</v>
+        <v>-56.902596</v>
       </c>
       <c r="O62">
-        <v>-19.26265599999999</v>
+        <v>-19.9159086</v>
       </c>
       <c r="P62">
-        <v>-35.77350399999999</v>
+        <v>-36.98668740000001</v>
       </c>
       <c r="Q62">
-        <v>-3.973503999999991</v>
+        <v>-5.186687400000011</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.291887084802987</v>
+        <v>0.2981970100543457</v>
       </c>
       <c r="T62">
-        <v>1.209117437600996</v>
+        <v>1.240120448821535</v>
       </c>
       <c r="U62">
         <v>0.2008</v>
       </c>
       <c r="V62">
-        <v>0.1779907445705791</v>
+        <v>0.175072863512045</v>
       </c>
       <c r="W62">
-        <v>0.1650594584902277</v>
+        <v>0.1656453690067814</v>
       </c>
       <c r="X62" t="inlineStr">
         <is>
@@ -6403,7 +6403,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>0.5085449844873688</v>
+        <v>0.5002081814629857</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -6411,22 +6411,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.2173405090153314</v>
+        <v>0.2423374181354083</v>
       </c>
       <c r="C63">
-        <v>58.35065415103622</v>
+        <v>-23.81530641937854</v>
       </c>
       <c r="D63">
-        <v>572.9456541510363</v>
+        <v>500.0746935806214</v>
       </c>
       <c r="E63">
-        <v>510.495</v>
+        <v>519.79</v>
       </c>
       <c r="F63">
-        <v>566.995</v>
+        <v>576.29</v>
       </c>
       <c r="G63">
         <v>52.4</v>
@@ -6447,45 +6447,45 @@
         <v>56.95</v>
       </c>
       <c r="M63">
-        <v>113.852596</v>
+        <v>135.889182</v>
       </c>
       <c r="N63">
-        <v>-56.902596</v>
+        <v>-78.939182</v>
       </c>
       <c r="O63">
-        <v>-19.9159086</v>
+        <v>-27.6287137</v>
       </c>
       <c r="P63">
-        <v>-36.98668740000001</v>
+        <v>-51.3104683</v>
       </c>
       <c r="Q63">
-        <v>-5.186687400000011</v>
+        <v>-19.51046830000001</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.2981970100543457</v>
+        <v>0.3094361658980834</v>
       </c>
       <c r="T63">
-        <v>1.240120448821535</v>
+        <v>1.295342604528966</v>
       </c>
       <c r="U63">
-        <v>0.2008</v>
+        <v>0.2358</v>
       </c>
       <c r="V63">
-        <v>0.175072863512045</v>
+        <v>0.1466820221200537</v>
       </c>
       <c r="W63">
-        <v>0.1656453690067814</v>
+        <v>0.2012123791840914</v>
       </c>
       <c r="X63" t="inlineStr">
         <is>
-          <t>C2/C</t>
+          <t>D2/D</t>
         </is>
       </c>
       <c r="Y63">
-        <v>0.5002081814629857</v>
+        <v>0.4190914917715819</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -6493,22 +6493,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.2423374181354083</v>
+        <v>0.2442374181354083</v>
       </c>
       <c r="C64">
-        <v>-23.81530641937854</v>
+        <v>-37.89842514583177</v>
       </c>
       <c r="D64">
-        <v>500.0746935806214</v>
+        <v>495.2865748541682</v>
       </c>
       <c r="E64">
-        <v>519.79</v>
+        <v>529.085</v>
       </c>
       <c r="F64">
-        <v>576.29</v>
+        <v>585.585</v>
       </c>
       <c r="G64">
         <v>52.4</v>
@@ -6529,37 +6529,37 @@
         <v>56.95</v>
       </c>
       <c r="M64">
-        <v>135.889182</v>
+        <v>138.080943</v>
       </c>
       <c r="N64">
-        <v>-78.939182</v>
+        <v>-81.13094300000002</v>
       </c>
       <c r="O64">
-        <v>-27.6287137</v>
+        <v>-28.39583005</v>
       </c>
       <c r="P64">
-        <v>-51.3104683</v>
+        <v>-52.73511295000002</v>
       </c>
       <c r="Q64">
-        <v>-19.51046830000001</v>
+        <v>-20.93511295000002</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.3094361658980834</v>
+        <v>0.3165614676791127</v>
       </c>
       <c r="T64">
-        <v>1.295342604528966</v>
+        <v>1.33035186411083</v>
       </c>
       <c r="U64">
         <v>0.2358</v>
       </c>
       <c r="V64">
-        <v>0.1466820221200537</v>
+        <v>0.144353736054656</v>
       </c>
       <c r="W64">
-        <v>0.2012123791840914</v>
+        <v>0.2017613890383121</v>
       </c>
       <c r="X64" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>0.4190914917715819</v>
+        <v>0.4124392458704457</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -6575,22 +6575,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.2442374181354083</v>
+        <v>0.2461374181354083</v>
       </c>
       <c r="C65">
-        <v>-37.89842514583177</v>
+        <v>-51.89072283979954</v>
       </c>
       <c r="D65">
-        <v>495.2865748541682</v>
+        <v>490.5892771602004</v>
       </c>
       <c r="E65">
-        <v>529.085</v>
+        <v>538.38</v>
       </c>
       <c r="F65">
-        <v>585.585</v>
+        <v>594.88</v>
       </c>
       <c r="G65">
         <v>52.4</v>
@@ -6611,37 +6611,37 @@
         <v>56.95</v>
       </c>
       <c r="M65">
-        <v>138.080943</v>
+        <v>140.272704</v>
       </c>
       <c r="N65">
-        <v>-81.13094300000002</v>
+        <v>-83.322704</v>
       </c>
       <c r="O65">
-        <v>-28.39583005</v>
+        <v>-29.1629464</v>
       </c>
       <c r="P65">
-        <v>-52.73511295000002</v>
+        <v>-54.15975760000001</v>
       </c>
       <c r="Q65">
-        <v>-20.93511295000002</v>
+        <v>-22.35975760000001</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.3165614676791127</v>
+        <v>0.324082619559088</v>
       </c>
       <c r="T65">
-        <v>1.33035186411083</v>
+        <v>1.367306082558353</v>
       </c>
       <c r="U65">
         <v>0.2358</v>
       </c>
       <c r="V65">
-        <v>0.144353736054656</v>
+        <v>0.142098208928802</v>
       </c>
       <c r="W65">
-        <v>0.2017613890383121</v>
+        <v>0.2022932423345885</v>
       </c>
       <c r="X65" t="inlineStr">
         <is>
@@ -6649,7 +6649,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>0.4124392458704457</v>
+        <v>0.40599488265372</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -6657,22 +6657,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.2461374181354083</v>
+        <v>0.2480374181354083</v>
       </c>
       <c r="C66">
-        <v>-51.89072283979954</v>
+        <v>-65.79475926440568</v>
       </c>
       <c r="D66">
-        <v>490.5892771602004</v>
+        <v>485.9802407355944</v>
       </c>
       <c r="E66">
-        <v>538.38</v>
+        <v>547.6750000000001</v>
       </c>
       <c r="F66">
-        <v>594.88</v>
+        <v>604.1750000000001</v>
       </c>
       <c r="G66">
         <v>52.4</v>
@@ -6693,37 +6693,37 @@
         <v>56.95</v>
       </c>
       <c r="M66">
-        <v>140.272704</v>
+        <v>142.464465</v>
       </c>
       <c r="N66">
-        <v>-83.322704</v>
+        <v>-85.51446500000002</v>
       </c>
       <c r="O66">
-        <v>-29.1629464</v>
+        <v>-29.93006275</v>
       </c>
       <c r="P66">
-        <v>-54.15975760000001</v>
+        <v>-55.58440225000001</v>
       </c>
       <c r="Q66">
-        <v>-22.35975760000001</v>
+        <v>-23.78440225000001</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.324082619559088</v>
+        <v>0.3320335515464905</v>
       </c>
       <c r="T66">
-        <v>1.367306082558353</v>
+        <v>1.406371970631449</v>
       </c>
       <c r="U66">
         <v>0.2358</v>
       </c>
       <c r="V66">
-        <v>0.142098208928802</v>
+        <v>0.1399120826375896</v>
       </c>
       <c r="W66">
-        <v>0.2022932423345885</v>
+        <v>0.2028087309140564</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
@@ -6731,7 +6731,7 @@
         </is>
       </c>
       <c r="Y66">
-        <v>0.40599488265372</v>
+        <v>0.3997488075359704</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -6739,22 +6739,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.2480374181354083</v>
+        <v>0.2499374181354083</v>
       </c>
       <c r="C67">
-        <v>-65.79475926440568</v>
+        <v>-79.61299888324481</v>
       </c>
       <c r="D67">
-        <v>485.9802407355944</v>
+        <v>481.4570011167552</v>
       </c>
       <c r="E67">
-        <v>547.6750000000001</v>
+        <v>556.97</v>
       </c>
       <c r="F67">
-        <v>604.1750000000001</v>
+        <v>613.47</v>
       </c>
       <c r="G67">
         <v>52.4</v>
@@ -6775,37 +6775,37 @@
         <v>56.95</v>
       </c>
       <c r="M67">
-        <v>142.464465</v>
+        <v>144.656226</v>
       </c>
       <c r="N67">
-        <v>-85.51446500000002</v>
+        <v>-87.706226</v>
       </c>
       <c r="O67">
-        <v>-29.93006275</v>
+        <v>-30.6971791</v>
       </c>
       <c r="P67">
-        <v>-55.58440225000001</v>
+        <v>-57.0090469</v>
       </c>
       <c r="Q67">
-        <v>-23.78440225000001</v>
+        <v>-25.2090469</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.3320335515464905</v>
+        <v>0.340452185415505</v>
       </c>
       <c r="T67">
-        <v>1.406371970631449</v>
+        <v>1.447735852120609</v>
       </c>
       <c r="U67">
         <v>0.2358</v>
       </c>
       <c r="V67">
-        <v>0.1399120826375896</v>
+        <v>0.1377922025976262</v>
       </c>
       <c r="W67">
-        <v>0.2028087309140564</v>
+        <v>0.2033085986274798</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
@@ -6813,7 +6813,7 @@
         </is>
       </c>
       <c r="Y67">
-        <v>0.3997488075359704</v>
+        <v>0.3936920074217891</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -6821,22 +6821,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.2499374181354083</v>
+        <v>0.2518374181354083</v>
       </c>
       <c r="C68">
-        <v>-79.61299888324481</v>
+        <v>-93.34781525446658</v>
       </c>
       <c r="D68">
-        <v>481.4570011167552</v>
+        <v>477.0171847455334</v>
       </c>
       <c r="E68">
-        <v>556.97</v>
+        <v>566.265</v>
       </c>
       <c r="F68">
-        <v>613.47</v>
+        <v>622.765</v>
       </c>
       <c r="G68">
         <v>52.4</v>
@@ -6857,37 +6857,37 @@
         <v>56.95</v>
       </c>
       <c r="M68">
-        <v>144.656226</v>
+        <v>146.847987</v>
       </c>
       <c r="N68">
-        <v>-87.706226</v>
+        <v>-89.89798699999999</v>
       </c>
       <c r="O68">
-        <v>-30.6971791</v>
+        <v>-31.46429544999999</v>
       </c>
       <c r="P68">
-        <v>-57.0090469</v>
+        <v>-58.43369154999999</v>
       </c>
       <c r="Q68">
-        <v>-25.2090469</v>
+        <v>-26.63369154999999</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.340452185415505</v>
+        <v>0.3493810395190051</v>
       </c>
       <c r="T68">
-        <v>1.447735852120609</v>
+        <v>1.491606635518203</v>
       </c>
       <c r="U68">
         <v>0.2358</v>
       </c>
       <c r="V68">
-        <v>0.1377922025976262</v>
+        <v>0.1357356025588556</v>
       </c>
       <c r="W68">
-        <v>0.2033085986274798</v>
+        <v>0.2037935449166219</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -6895,7 +6895,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.3936920074217891</v>
+        <v>0.3878160073110162</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -6903,22 +6903,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.2518374181354083</v>
+        <v>0.2537374181354083</v>
       </c>
       <c r="C69">
-        <v>-93.34781525446658</v>
+        <v>-107.0014951839554</v>
       </c>
       <c r="D69">
-        <v>477.0171847455334</v>
+        <v>472.6585048160447</v>
       </c>
       <c r="E69">
-        <v>566.265</v>
+        <v>575.5600000000001</v>
       </c>
       <c r="F69">
-        <v>622.765</v>
+        <v>632.0600000000001</v>
       </c>
       <c r="G69">
         <v>52.4</v>
@@ -6939,37 +6939,37 @@
         <v>56.95</v>
       </c>
       <c r="M69">
-        <v>146.847987</v>
+        <v>149.039748</v>
       </c>
       <c r="N69">
-        <v>-89.89798699999999</v>
+        <v>-92.08974800000003</v>
       </c>
       <c r="O69">
-        <v>-31.46429544999999</v>
+        <v>-32.23141180000001</v>
       </c>
       <c r="P69">
-        <v>-58.43369154999999</v>
+        <v>-59.85833620000002</v>
       </c>
       <c r="Q69">
-        <v>-26.63369154999999</v>
+        <v>-28.05833620000002</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.3493810395190051</v>
+        <v>0.3588679470039741</v>
       </c>
       <c r="T69">
-        <v>1.491606635518203</v>
+        <v>1.538219342878147</v>
       </c>
       <c r="U69">
         <v>0.2358</v>
       </c>
       <c r="V69">
-        <v>0.1357356025588556</v>
+        <v>0.1337394907565195</v>
       </c>
       <c r="W69">
-        <v>0.2037935449166219</v>
+        <v>0.2042642280796127</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -6977,7 +6977,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.3878160073110162</v>
+        <v>0.3821128307329129</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -6985,22 +6985,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.2537374181354083</v>
+        <v>0.2556374181354084</v>
       </c>
       <c r="C70">
-        <v>-107.0014951839554</v>
+        <v>-120.5762426528789</v>
       </c>
       <c r="D70">
-        <v>472.6585048160447</v>
+        <v>468.3787573471211</v>
       </c>
       <c r="E70">
-        <v>575.5600000000001</v>
+        <v>584.855</v>
       </c>
       <c r="F70">
-        <v>632.0600000000001</v>
+        <v>641.355</v>
       </c>
       <c r="G70">
         <v>52.4</v>
@@ -7021,37 +7021,37 @@
         <v>56.95</v>
       </c>
       <c r="M70">
-        <v>149.039748</v>
+        <v>151.231509</v>
       </c>
       <c r="N70">
-        <v>-92.08974800000003</v>
+        <v>-94.28150900000001</v>
       </c>
       <c r="O70">
-        <v>-32.23141180000001</v>
+        <v>-32.99852815000001</v>
       </c>
       <c r="P70">
-        <v>-59.85833620000002</v>
+        <v>-61.28298085000001</v>
       </c>
       <c r="Q70">
-        <v>-28.05833620000002</v>
+        <v>-29.48298085000001</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.3588679470039741</v>
+        <v>0.3689669130363603</v>
       </c>
       <c r="T70">
-        <v>1.538219342878147</v>
+        <v>1.587839321680668</v>
       </c>
       <c r="U70">
         <v>0.2358</v>
       </c>
       <c r="V70">
-        <v>0.1337394907565195</v>
+        <v>0.1318012372672946</v>
       </c>
       <c r="W70">
-        <v>0.2042642280796127</v>
+        <v>0.204721268252372</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -7059,7 +7059,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.3821128307329129</v>
+        <v>0.3765749636208418</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -7067,22 +7067,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.2556374181354084</v>
+        <v>0.2575374181354083</v>
       </c>
       <c r="C71">
-        <v>-120.5762426528789</v>
+        <v>-134.0741825337763</v>
       </c>
       <c r="D71">
-        <v>468.3787573471211</v>
+        <v>464.1758174662238</v>
       </c>
       <c r="E71">
-        <v>584.855</v>
+        <v>594.1500000000001</v>
       </c>
       <c r="F71">
-        <v>641.355</v>
+        <v>650.6500000000001</v>
       </c>
       <c r="G71">
         <v>52.4</v>
@@ -7103,37 +7103,37 @@
         <v>56.95</v>
       </c>
       <c r="M71">
-        <v>151.231509</v>
+        <v>153.42327</v>
       </c>
       <c r="N71">
-        <v>-94.28150900000001</v>
+        <v>-96.47327000000003</v>
       </c>
       <c r="O71">
-        <v>-32.99852815000001</v>
+        <v>-33.76564450000001</v>
       </c>
       <c r="P71">
-        <v>-61.28298085000001</v>
+        <v>-62.70762550000002</v>
       </c>
       <c r="Q71">
-        <v>-29.48298085000001</v>
+        <v>-30.90762550000002</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.3689669130363603</v>
+        <v>0.3797391434709056</v>
       </c>
       <c r="T71">
-        <v>1.587839321680668</v>
+        <v>1.640767299070024</v>
       </c>
       <c r="U71">
         <v>0.2358</v>
       </c>
       <c r="V71">
-        <v>0.1318012372672946</v>
+        <v>0.1299183624491904</v>
       </c>
       <c r="W71">
-        <v>0.204721268252372</v>
+        <v>0.2051652501344809</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -7141,7 +7141,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.3765749636208418</v>
+        <v>0.371195321283401</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -7149,22 +7149,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.2575374181354083</v>
+        <v>0.2594374181354083</v>
       </c>
       <c r="C72">
-        <v>-134.0741825337763</v>
+        <v>-147.4973641083487</v>
       </c>
       <c r="D72">
-        <v>464.1758174662238</v>
+        <v>460.0476358916513</v>
       </c>
       <c r="E72">
-        <v>594.1500000000001</v>
+        <v>603.4450000000001</v>
       </c>
       <c r="F72">
-        <v>650.6500000000001</v>
+        <v>659.9450000000001</v>
       </c>
       <c r="G72">
         <v>52.4</v>
@@ -7185,37 +7185,37 @@
         <v>56.95</v>
       </c>
       <c r="M72">
-        <v>153.42327</v>
+        <v>155.615031</v>
       </c>
       <c r="N72">
-        <v>-96.47327000000003</v>
+        <v>-98.66503100000001</v>
       </c>
       <c r="O72">
-        <v>-33.76564450000001</v>
+        <v>-34.53276085</v>
       </c>
       <c r="P72">
-        <v>-62.70762550000002</v>
+        <v>-64.13227015000001</v>
       </c>
       <c r="Q72">
-        <v>-30.90762550000002</v>
+        <v>-32.33227015000001</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.3797391434709056</v>
+        <v>0.3912542863492128</v>
       </c>
       <c r="T72">
-        <v>1.640767299070024</v>
+        <v>1.697345481796577</v>
       </c>
       <c r="U72">
         <v>0.2358</v>
       </c>
       <c r="V72">
-        <v>0.1299183624491904</v>
+        <v>0.1280885263583567</v>
       </c>
       <c r="W72">
-        <v>0.2051652501344809</v>
+        <v>0.2055967254846995</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -7223,7 +7223,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.371195321283401</v>
+        <v>0.3659672181667335</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -7231,22 +7231,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.2594374181354083</v>
+        <v>0.2613374181354083</v>
       </c>
       <c r="C73">
-        <v>-147.4973641083485</v>
+        <v>-160.8477643991928</v>
       </c>
       <c r="D73">
-        <v>460.0476358916515</v>
+        <v>455.9922356008072</v>
       </c>
       <c r="E73">
-        <v>603.4449999999999</v>
+        <v>612.74</v>
       </c>
       <c r="F73">
-        <v>659.9449999999999</v>
+        <v>669.24</v>
       </c>
       <c r="G73">
         <v>52.4</v>
@@ -7267,37 +7267,37 @@
         <v>56.95</v>
       </c>
       <c r="M73">
-        <v>155.615031</v>
+        <v>157.806792</v>
       </c>
       <c r="N73">
-        <v>-98.66503099999998</v>
+        <v>-100.856792</v>
       </c>
       <c r="O73">
-        <v>-34.53276085</v>
+        <v>-35.2998772</v>
       </c>
       <c r="P73">
-        <v>-64.13227014999998</v>
+        <v>-65.5569148</v>
       </c>
       <c r="Q73">
-        <v>-32.33227014999999</v>
+        <v>-33.7569148</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.3912542863492126</v>
+        <v>0.4035919394331131</v>
       </c>
       <c r="T73">
-        <v>1.697345481796576</v>
+        <v>1.757964963289311</v>
       </c>
       <c r="U73">
         <v>0.2358</v>
       </c>
       <c r="V73">
-        <v>0.1280885263583567</v>
+        <v>0.126309519047824</v>
       </c>
       <c r="W73">
-        <v>0.2055967254846995</v>
+        <v>0.2060162154085231</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -7305,7 +7305,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.3659672181667336</v>
+        <v>0.3608843401366401</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -7313,22 +7313,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.2613374181354083</v>
+        <v>0.2632374181354083</v>
       </c>
       <c r="C74">
-        <v>-160.8477643991928</v>
+        <v>-174.1272913268533</v>
       </c>
       <c r="D74">
-        <v>455.9922356008072</v>
+        <v>452.0077086731467</v>
       </c>
       <c r="E74">
-        <v>612.74</v>
+        <v>622.035</v>
       </c>
       <c r="F74">
-        <v>669.24</v>
+        <v>678.535</v>
       </c>
       <c r="G74">
         <v>52.4</v>
@@ -7349,37 +7349,37 @@
         <v>56.95</v>
       </c>
       <c r="M74">
-        <v>157.806792</v>
+        <v>159.998553</v>
       </c>
       <c r="N74">
-        <v>-100.856792</v>
+        <v>-103.048553</v>
       </c>
       <c r="O74">
-        <v>-35.2998772</v>
+        <v>-36.06699354999999</v>
       </c>
       <c r="P74">
-        <v>-65.5569148</v>
+        <v>-66.98155944999999</v>
       </c>
       <c r="Q74">
-        <v>-33.7569148</v>
+        <v>-35.18155944999999</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.4035919394331131</v>
+        <v>0.4168434927454506</v>
       </c>
       <c r="T74">
-        <v>1.757964963289311</v>
+        <v>1.82307477674447</v>
       </c>
       <c r="U74">
         <v>0.2358</v>
       </c>
       <c r="V74">
-        <v>0.126309519047824</v>
+        <v>0.1245792516636072</v>
       </c>
       <c r="W74">
-        <v>0.2060162154085231</v>
+        <v>0.2064242124577214</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -7387,7 +7387,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.3608843401366401</v>
+        <v>0.3559407190388778</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -7395,22 +7395,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.2632374181354083</v>
+        <v>0.2651374181354084</v>
       </c>
       <c r="C75">
-        <v>-174.1272913268533</v>
+        <v>-187.3377867027898</v>
       </c>
       <c r="D75">
-        <v>452.0077086731467</v>
+        <v>448.0922132972103</v>
       </c>
       <c r="E75">
-        <v>622.035</v>
+        <v>631.33</v>
       </c>
       <c r="F75">
-        <v>678.535</v>
+        <v>687.83</v>
       </c>
       <c r="G75">
         <v>52.4</v>
@@ -7431,37 +7431,37 @@
         <v>56.95</v>
       </c>
       <c r="M75">
-        <v>159.998553</v>
+        <v>162.190314</v>
       </c>
       <c r="N75">
-        <v>-103.048553</v>
+        <v>-105.240314</v>
       </c>
       <c r="O75">
-        <v>-36.06699354999999</v>
+        <v>-36.83410990000001</v>
       </c>
       <c r="P75">
-        <v>-66.98155944999999</v>
+        <v>-68.40620410000002</v>
       </c>
       <c r="Q75">
-        <v>-35.18155944999999</v>
+        <v>-36.60620410000003</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.4168434927454506</v>
+        <v>0.4311143963125834</v>
       </c>
       <c r="T75">
-        <v>1.82307477674447</v>
+        <v>1.893193037388489</v>
       </c>
       <c r="U75">
         <v>0.2358</v>
       </c>
       <c r="V75">
-        <v>0.1245792516636072</v>
+        <v>0.1228957482627477</v>
       </c>
       <c r="W75">
-        <v>0.2064242124577214</v>
+        <v>0.2068211825596441</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.3559407190388778</v>
+        <v>0.3511307093221362</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -7477,22 +7477,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.2651374181354084</v>
+        <v>0.2670374181354083</v>
       </c>
       <c r="C76">
-        <v>-187.3377867027898</v>
+        <v>-200.4810290681187</v>
       </c>
       <c r="D76">
-        <v>448.0922132972103</v>
+        <v>444.2439709318813</v>
       </c>
       <c r="E76">
-        <v>631.33</v>
+        <v>640.625</v>
       </c>
       <c r="F76">
-        <v>687.83</v>
+        <v>697.125</v>
       </c>
       <c r="G76">
         <v>52.4</v>
@@ -7513,37 +7513,37 @@
         <v>56.95</v>
       </c>
       <c r="M76">
-        <v>162.190314</v>
+        <v>164.382075</v>
       </c>
       <c r="N76">
-        <v>-105.240314</v>
+        <v>-107.432075</v>
       </c>
       <c r="O76">
-        <v>-36.83410990000001</v>
+        <v>-37.60122625</v>
       </c>
       <c r="P76">
-        <v>-68.40620410000002</v>
+        <v>-69.83084875</v>
       </c>
       <c r="Q76">
-        <v>-36.60620410000003</v>
+        <v>-38.03084875</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.4311143963125834</v>
+        <v>0.4465269721650867</v>
       </c>
       <c r="T76">
-        <v>1.893193037388489</v>
+        <v>1.968920758884028</v>
       </c>
       <c r="U76">
         <v>0.2358</v>
       </c>
       <c r="V76">
-        <v>0.1228957482627477</v>
+        <v>0.121257138285911</v>
       </c>
       <c r="W76">
-        <v>0.2068211825596441</v>
+        <v>0.2072075667921822</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -7551,7 +7551,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.3511307093221362</v>
+        <v>0.3464489665311744</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -7559,22 +7559,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.2670374181354083</v>
+        <v>0.2689374181354083</v>
       </c>
       <c r="C77">
-        <v>-200.4810290681187</v>
+        <v>-213.5587363873294</v>
       </c>
       <c r="D77">
-        <v>444.2439709318813</v>
+        <v>440.4612636126706</v>
       </c>
       <c r="E77">
-        <v>640.625</v>
+        <v>649.92</v>
       </c>
       <c r="F77">
-        <v>697.125</v>
+        <v>706.42</v>
       </c>
       <c r="G77">
         <v>52.4</v>
@@ -7595,37 +7595,37 @@
         <v>56.95</v>
       </c>
       <c r="M77">
-        <v>164.382075</v>
+        <v>166.573836</v>
       </c>
       <c r="N77">
-        <v>-107.432075</v>
+        <v>-109.623836</v>
       </c>
       <c r="O77">
-        <v>-37.60122625</v>
+        <v>-38.3683426</v>
       </c>
       <c r="P77">
-        <v>-69.83084875</v>
+        <v>-71.25549340000001</v>
       </c>
       <c r="Q77">
-        <v>-38.03084875</v>
+        <v>-39.45549340000001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.4465269721650867</v>
+        <v>0.463223929338632</v>
       </c>
       <c r="T77">
-        <v>1.968920758884028</v>
+        <v>2.05095912383753</v>
       </c>
       <c r="U77">
         <v>0.2358</v>
       </c>
       <c r="V77">
-        <v>0.121257138285911</v>
+        <v>0.1196616496242543</v>
       </c>
       <c r="W77">
-        <v>0.2072075667921822</v>
+        <v>0.2075837830186008</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -7633,7 +7633,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.3464489665311744</v>
+        <v>0.3418904274978695</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -7641,22 +7641,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.2689374181354083</v>
+        <v>0.2708374181354083</v>
       </c>
       <c r="C78">
-        <v>-213.5587363873294</v>
+        <v>-226.5725686055363</v>
       </c>
       <c r="D78">
-        <v>440.4612636126706</v>
+        <v>436.7424313944637</v>
       </c>
       <c r="E78">
-        <v>649.92</v>
+        <v>659.215</v>
       </c>
       <c r="F78">
-        <v>706.42</v>
+        <v>715.715</v>
       </c>
       <c r="G78">
         <v>52.4</v>
@@ -7677,37 +7677,37 @@
         <v>56.95</v>
       </c>
       <c r="M78">
-        <v>166.573836</v>
+        <v>168.765597</v>
       </c>
       <c r="N78">
-        <v>-109.623836</v>
+        <v>-111.815597</v>
       </c>
       <c r="O78">
-        <v>-38.3683426</v>
+        <v>-39.13545895</v>
       </c>
       <c r="P78">
-        <v>-71.25549340000001</v>
+        <v>-72.68013805000001</v>
       </c>
       <c r="Q78">
-        <v>-39.45549340000001</v>
+        <v>-40.88013805000001</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.463223929338632</v>
+        <v>0.481372795831616</v>
       </c>
       <c r="T78">
-        <v>2.05095912383753</v>
+        <v>2.140131259656552</v>
       </c>
       <c r="U78">
         <v>0.2358</v>
       </c>
       <c r="V78">
-        <v>0.1196616496242543</v>
+        <v>0.1181076022265367</v>
       </c>
       <c r="W78">
-        <v>0.2075837830186008</v>
+        <v>0.2079502273949826</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -7715,7 +7715,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.3418904274978695</v>
+        <v>0.3374502920758192</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -7723,22 +7723,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.2708374181354083</v>
+        <v>0.2727374181354083</v>
       </c>
       <c r="C79">
-        <v>-226.5725686055363</v>
+        <v>-239.5241300772736</v>
       </c>
       <c r="D79">
-        <v>436.7424313944637</v>
+        <v>433.0858699227264</v>
       </c>
       <c r="E79">
-        <v>659.215</v>
+        <v>668.51</v>
       </c>
       <c r="F79">
-        <v>715.715</v>
+        <v>725.01</v>
       </c>
       <c r="G79">
         <v>52.4</v>
@@ -7759,37 +7759,37 @@
         <v>56.95</v>
       </c>
       <c r="M79">
-        <v>168.765597</v>
+        <v>170.957358</v>
       </c>
       <c r="N79">
-        <v>-111.815597</v>
+        <v>-114.007358</v>
       </c>
       <c r="O79">
-        <v>-39.13545895</v>
+        <v>-39.9025753</v>
       </c>
       <c r="P79">
-        <v>-72.68013805000001</v>
+        <v>-74.1047827</v>
       </c>
       <c r="Q79">
-        <v>-40.88013805000001</v>
+        <v>-42.3047827</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.481372795831616</v>
+        <v>0.5011715592785077</v>
       </c>
       <c r="T79">
-        <v>2.140131259656552</v>
+        <v>2.237409953277305</v>
       </c>
       <c r="U79">
         <v>0.2358</v>
       </c>
       <c r="V79">
-        <v>0.1181076022265367</v>
+        <v>0.1165934021979914</v>
       </c>
       <c r="W79">
-        <v>0.2079502273949826</v>
+        <v>0.2083072757617136</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
@@ -7797,7 +7797,7 @@
         </is>
       </c>
       <c r="Y79">
-        <v>0.3374502920758192</v>
+        <v>0.3331240062799754</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -7805,22 +7805,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.2727374181354083</v>
+        <v>0.2746374181354083</v>
       </c>
       <c r="C80">
-        <v>-239.5241300772736</v>
+        <v>-252.4149718742926</v>
       </c>
       <c r="D80">
-        <v>433.0858699227264</v>
+        <v>429.4900281257075</v>
       </c>
       <c r="E80">
-        <v>668.51</v>
+        <v>677.8050000000001</v>
       </c>
       <c r="F80">
-        <v>725.01</v>
+        <v>734.3050000000001</v>
       </c>
       <c r="G80">
         <v>52.4</v>
@@ -7841,37 +7841,37 @@
         <v>56.95</v>
       </c>
       <c r="M80">
-        <v>170.957358</v>
+        <v>173.149119</v>
       </c>
       <c r="N80">
-        <v>-114.007358</v>
+        <v>-116.199119</v>
       </c>
       <c r="O80">
-        <v>-39.9025753</v>
+        <v>-40.66969165</v>
       </c>
       <c r="P80">
-        <v>-74.1047827</v>
+        <v>-75.52942735000001</v>
       </c>
       <c r="Q80">
-        <v>-42.3047827</v>
+        <v>-43.72942735000001</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.5011715592785077</v>
+        <v>0.5228559192441509</v>
       </c>
       <c r="T80">
-        <v>2.237409953277305</v>
+        <v>2.343953284385748</v>
       </c>
       <c r="U80">
         <v>0.2358</v>
       </c>
       <c r="V80">
-        <v>0.1165934021979914</v>
+        <v>0.1151175363473839</v>
       </c>
       <c r="W80">
-        <v>0.2083072757617136</v>
+        <v>0.2086552849292869</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -7879,7 +7879,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.3331240062799754</v>
+        <v>0.3289072467068112</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -7887,22 +7887,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.2746374181354083</v>
+        <v>0.2765374181354083</v>
       </c>
       <c r="C81">
-        <v>-252.4149718742926</v>
+        <v>-265.2465939793382</v>
       </c>
       <c r="D81">
-        <v>429.4900281257075</v>
+        <v>425.9534060206618</v>
       </c>
       <c r="E81">
-        <v>677.8050000000001</v>
+        <v>687.1</v>
       </c>
       <c r="F81">
-        <v>734.3050000000001</v>
+        <v>743.6</v>
       </c>
       <c r="G81">
         <v>52.4</v>
@@ -7923,37 +7923,37 @@
         <v>56.95</v>
       </c>
       <c r="M81">
-        <v>173.149119</v>
+        <v>175.34088</v>
       </c>
       <c r="N81">
-        <v>-116.199119</v>
+        <v>-118.39088</v>
       </c>
       <c r="O81">
-        <v>-40.66969165</v>
+        <v>-41.436808</v>
       </c>
       <c r="P81">
-        <v>-75.52942735000001</v>
+        <v>-76.954072</v>
       </c>
       <c r="Q81">
-        <v>-43.72942735000001</v>
+        <v>-45.154072</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.5228559192441509</v>
+        <v>0.5467087152063584</v>
       </c>
       <c r="T81">
-        <v>2.343953284385748</v>
+        <v>2.461150948605036</v>
       </c>
       <c r="U81">
         <v>0.2358</v>
       </c>
       <c r="V81">
-        <v>0.1151175363473839</v>
+        <v>0.1136785671430416</v>
       </c>
       <c r="W81">
-        <v>0.2086552849292869</v>
+        <v>0.2089945938676708</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -7961,7 +7961,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.3289072467068112</v>
+        <v>0.324795906122976</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -7969,22 +7969,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.2765374181354083</v>
+        <v>0.2784374181354083</v>
       </c>
       <c r="C82">
-        <v>-265.2465939793382</v>
+        <v>-278.0204473724249</v>
       </c>
       <c r="D82">
-        <v>425.9534060206618</v>
+        <v>422.4745526275752</v>
       </c>
       <c r="E82">
-        <v>687.1</v>
+        <v>696.3950000000001</v>
       </c>
       <c r="F82">
-        <v>743.6</v>
+        <v>752.8950000000001</v>
       </c>
       <c r="G82">
         <v>52.4</v>
@@ -8005,37 +8005,37 @@
         <v>56.95</v>
       </c>
       <c r="M82">
-        <v>175.34088</v>
+        <v>177.532641</v>
       </c>
       <c r="N82">
-        <v>-118.39088</v>
+        <v>-120.582641</v>
       </c>
       <c r="O82">
-        <v>-41.436808</v>
+        <v>-42.20392435000001</v>
       </c>
       <c r="P82">
-        <v>-76.954072</v>
+        <v>-78.37871665000003</v>
       </c>
       <c r="Q82">
-        <v>-45.154072</v>
+        <v>-46.57871665000003</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.5467087152063584</v>
+        <v>0.5730723317961668</v>
       </c>
       <c r="T82">
-        <v>2.461150948605036</v>
+        <v>2.590685209057932</v>
       </c>
       <c r="U82">
         <v>0.2358</v>
       </c>
       <c r="V82">
-        <v>0.1136785671430416</v>
+        <v>0.1122751280425102</v>
       </c>
       <c r="W82">
-        <v>0.2089945938676708</v>
+        <v>0.2093255248075761</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -8043,7 +8043,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.324795906122976</v>
+        <v>0.3207860801214577</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -8051,22 +8051,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2784374181354083</v>
+        <v>0.2803374181354083</v>
       </c>
       <c r="C83">
-        <v>-278.0204473724249</v>
+        <v>-290.7379360157037</v>
       </c>
       <c r="D83">
-        <v>422.4745526275752</v>
+        <v>419.0520639842964</v>
       </c>
       <c r="E83">
-        <v>696.3950000000001</v>
+        <v>705.6900000000001</v>
       </c>
       <c r="F83">
-        <v>752.8950000000001</v>
+        <v>762.1900000000001</v>
       </c>
       <c r="G83">
         <v>52.4</v>
@@ -8087,37 +8087,37 @@
         <v>56.95</v>
       </c>
       <c r="M83">
-        <v>177.532641</v>
+        <v>179.724402</v>
       </c>
       <c r="N83">
-        <v>-120.582641</v>
+        <v>-122.774402</v>
       </c>
       <c r="O83">
-        <v>-42.20392435000001</v>
+        <v>-42.9710407</v>
       </c>
       <c r="P83">
-        <v>-78.37871665000003</v>
+        <v>-79.80336130000002</v>
       </c>
       <c r="Q83">
-        <v>-46.57871665000003</v>
+        <v>-48.00336130000002</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.5730723317961668</v>
+        <v>0.602365239118176</v>
       </c>
       <c r="T83">
-        <v>2.590685209057932</v>
+        <v>2.734612165116706</v>
       </c>
       <c r="U83">
         <v>0.2358</v>
       </c>
       <c r="V83">
-        <v>0.1122751280425102</v>
+        <v>0.110905919163943</v>
       </c>
       <c r="W83">
-        <v>0.2093255248075761</v>
+        <v>0.2096483842611422</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -8125,7 +8125,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.3207860801214577</v>
+        <v>0.3168740547541229</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -8133,22 +8133,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2803374181354083</v>
+        <v>0.2822374181354083</v>
       </c>
       <c r="C84">
-        <v>-290.7379360157037</v>
+        <v>-303.4004187426305</v>
       </c>
       <c r="D84">
-        <v>419.0520639842964</v>
+        <v>415.6845812573695</v>
       </c>
       <c r="E84">
-        <v>705.6900000000001</v>
+        <v>714.985</v>
       </c>
       <c r="F84">
-        <v>762.1900000000001</v>
+        <v>771.485</v>
       </c>
       <c r="G84">
         <v>52.4</v>
@@ -8169,37 +8169,37 @@
         <v>56.95</v>
       </c>
       <c r="M84">
-        <v>179.724402</v>
+        <v>181.916163</v>
       </c>
       <c r="N84">
-        <v>-122.774402</v>
+        <v>-124.966163</v>
       </c>
       <c r="O84">
-        <v>-42.9710407</v>
+        <v>-43.73815705</v>
       </c>
       <c r="P84">
-        <v>-79.80336130000002</v>
+        <v>-81.22800595000001</v>
       </c>
       <c r="Q84">
-        <v>-48.00336130000002</v>
+        <v>-49.42800595000001</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.602365239118176</v>
+        <v>0.63510437083101</v>
       </c>
       <c r="T84">
-        <v>2.734612165116706</v>
+        <v>2.895471704241219</v>
       </c>
       <c r="U84">
         <v>0.2358</v>
       </c>
       <c r="V84">
-        <v>0.110905919163943</v>
+        <v>0.1095697032704015</v>
       </c>
       <c r="W84">
-        <v>0.2096483842611422</v>
+        <v>0.2099634639688393</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -8207,7 +8207,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.3168740547541229</v>
+        <v>0.3130562950582901</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -8215,22 +8215,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2822374181354083</v>
+        <v>0.2841374181354083</v>
       </c>
       <c r="C85">
-        <v>-303.4004187426305</v>
+        <v>-316.0092110567702</v>
       </c>
       <c r="D85">
-        <v>415.6845812573695</v>
+        <v>412.3707889432299</v>
       </c>
       <c r="E85">
-        <v>714.985</v>
+        <v>724.2800000000001</v>
       </c>
       <c r="F85">
-        <v>771.485</v>
+        <v>780.7800000000001</v>
       </c>
       <c r="G85">
         <v>52.4</v>
@@ -8251,37 +8251,37 @@
         <v>56.95</v>
       </c>
       <c r="M85">
-        <v>181.916163</v>
+        <v>184.107924</v>
       </c>
       <c r="N85">
-        <v>-124.966163</v>
+        <v>-127.157924</v>
       </c>
       <c r="O85">
-        <v>-43.73815705</v>
+        <v>-44.50527340000001</v>
       </c>
       <c r="P85">
-        <v>-81.22800595000001</v>
+        <v>-82.65265060000002</v>
       </c>
       <c r="Q85">
-        <v>-49.42800595000001</v>
+        <v>-50.85265060000002</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.63510437083101</v>
+        <v>0.6719358940079483</v>
       </c>
       <c r="T85">
-        <v>2.895471704241219</v>
+        <v>3.076438685756296</v>
       </c>
       <c r="U85">
         <v>0.2358</v>
       </c>
       <c r="V85">
-        <v>0.1095697032704015</v>
+        <v>0.108265302040992</v>
       </c>
       <c r="W85">
-        <v>0.2099634639688393</v>
+        <v>0.2102710417787341</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -8289,7 +8289,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.3130562950582901</v>
+        <v>0.3093294344028342</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -8297,22 +8297,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2841374181354083</v>
+        <v>0.2860374181354083</v>
       </c>
       <c r="C86">
-        <v>-316.00921105677</v>
+        <v>-328.5655868452433</v>
       </c>
       <c r="D86">
-        <v>412.37078894323</v>
+        <v>409.1094131547566</v>
       </c>
       <c r="E86">
-        <v>724.28</v>
+        <v>733.5749999999999</v>
       </c>
       <c r="F86">
-        <v>780.78</v>
+        <v>790.0749999999999</v>
       </c>
       <c r="G86">
         <v>52.4</v>
@@ -8333,37 +8333,37 @@
         <v>56.95</v>
       </c>
       <c r="M86">
-        <v>184.107924</v>
+        <v>186.299685</v>
       </c>
       <c r="N86">
-        <v>-127.157924</v>
+        <v>-129.349685</v>
       </c>
       <c r="O86">
-        <v>-44.50527339999999</v>
+        <v>-45.27238974999999</v>
       </c>
       <c r="P86">
-        <v>-82.6526506</v>
+        <v>-84.07729524999998</v>
       </c>
       <c r="Q86">
-        <v>-50.8526506</v>
+        <v>-52.27729524999998</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.6719358940079477</v>
+        <v>0.713678286941811</v>
       </c>
       <c r="T86">
-        <v>3.076438685756294</v>
+        <v>3.281534598140047</v>
       </c>
       <c r="U86">
         <v>0.2358</v>
       </c>
       <c r="V86">
-        <v>0.108265302040992</v>
+        <v>0.1069915926052156</v>
       </c>
       <c r="W86">
-        <v>0.2102710417787341</v>
+        <v>0.2105713824636902</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -8371,7 +8371,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.3093294344028343</v>
+        <v>0.3056902645863304</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -8379,22 +8379,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2860374181354083</v>
+        <v>0.2879374181354083</v>
       </c>
       <c r="C87">
-        <v>-328.5655868452433</v>
+        <v>-341.0707800115029</v>
       </c>
       <c r="D87">
-        <v>409.1094131547566</v>
+        <v>405.8992199884971</v>
       </c>
       <c r="E87">
-        <v>733.5749999999999</v>
+        <v>742.87</v>
       </c>
       <c r="F87">
-        <v>790.0749999999999</v>
+        <v>799.37</v>
       </c>
       <c r="G87">
         <v>52.4</v>
@@ -8415,37 +8415,37 @@
         <v>56.95</v>
       </c>
       <c r="M87">
-        <v>186.299685</v>
+        <v>188.491446</v>
       </c>
       <c r="N87">
-        <v>-129.349685</v>
+        <v>-131.541446</v>
       </c>
       <c r="O87">
-        <v>-45.27238974999999</v>
+        <v>-46.0395061</v>
       </c>
       <c r="P87">
-        <v>-84.07729524999998</v>
+        <v>-85.50193990000001</v>
       </c>
       <c r="Q87">
-        <v>-52.27729524999998</v>
+        <v>-53.70193990000001</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.713678286941811</v>
+        <v>0.761383878866226</v>
       </c>
       <c r="T87">
-        <v>3.281534598140047</v>
+        <v>3.515929926578621</v>
       </c>
       <c r="U87">
         <v>0.2358</v>
       </c>
       <c r="V87">
-        <v>0.1069915926052156</v>
+        <v>0.1057475043191085</v>
       </c>
       <c r="W87">
-        <v>0.2105713824636902</v>
+        <v>0.2108647384815542</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -8453,7 +8453,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.3056902645863304</v>
+        <v>0.3021357266260242</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -8461,22 +8461,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2879374181354083</v>
+        <v>0.2898374181354083</v>
       </c>
       <c r="C88">
-        <v>-341.0707800115029</v>
+        <v>-353.5259860318363</v>
       </c>
       <c r="D88">
-        <v>405.8992199884971</v>
+        <v>402.7390139681636</v>
       </c>
       <c r="E88">
-        <v>742.87</v>
+        <v>752.165</v>
       </c>
       <c r="F88">
-        <v>799.37</v>
+        <v>808.665</v>
       </c>
       <c r="G88">
         <v>52.4</v>
@@ -8497,37 +8497,37 @@
         <v>56.95</v>
       </c>
       <c r="M88">
-        <v>188.491446</v>
+        <v>190.683207</v>
       </c>
       <c r="N88">
-        <v>-131.541446</v>
+        <v>-133.733207</v>
       </c>
       <c r="O88">
-        <v>-46.0395061</v>
+        <v>-46.80662244999999</v>
       </c>
       <c r="P88">
-        <v>-85.50193990000001</v>
+        <v>-86.92658455</v>
       </c>
       <c r="Q88">
-        <v>-53.70193990000001</v>
+        <v>-55.12658455</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.761383878866226</v>
+        <v>0.8164287926251667</v>
       </c>
       <c r="T88">
-        <v>3.515929926578621</v>
+        <v>3.786386074776977</v>
       </c>
       <c r="U88">
         <v>0.2358</v>
       </c>
       <c r="V88">
-        <v>0.1057475043191085</v>
+        <v>0.1045320157637164</v>
       </c>
       <c r="W88">
-        <v>0.2108647384815542</v>
+        <v>0.2111513506829157</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -8535,7 +8535,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.3021357266260242</v>
+        <v>0.2986629021820469</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -8543,22 +8543,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2898374181354083</v>
+        <v>0.2917374181354083</v>
       </c>
       <c r="C89">
-        <v>-353.5259860318363</v>
+        <v>-365.9323634397191</v>
       </c>
       <c r="D89">
-        <v>402.7390139681636</v>
+        <v>399.627636560281</v>
       </c>
       <c r="E89">
-        <v>752.165</v>
+        <v>761.46</v>
       </c>
       <c r="F89">
-        <v>808.665</v>
+        <v>817.96</v>
       </c>
       <c r="G89">
         <v>52.4</v>
@@ -8579,37 +8579,37 @@
         <v>56.95</v>
       </c>
       <c r="M89">
-        <v>190.683207</v>
+        <v>192.874968</v>
       </c>
       <c r="N89">
-        <v>-133.733207</v>
+        <v>-135.924968</v>
       </c>
       <c r="O89">
-        <v>-46.80662244999999</v>
+        <v>-47.57373880000001</v>
       </c>
       <c r="P89">
-        <v>-86.92658455</v>
+        <v>-88.35122920000003</v>
       </c>
       <c r="Q89">
-        <v>-55.12658455</v>
+        <v>-56.55122920000004</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.8164287926251667</v>
+        <v>0.880647858677264</v>
       </c>
       <c r="T89">
-        <v>3.786386074776977</v>
+        <v>4.10191824767506</v>
       </c>
       <c r="U89">
         <v>0.2358</v>
       </c>
       <c r="V89">
-        <v>0.1045320157637164</v>
+        <v>0.1033441519482196</v>
       </c>
       <c r="W89">
-        <v>0.2111513506829157</v>
+        <v>0.2114314489706098</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -8617,7 +8617,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.2986629021820469</v>
+        <v>0.2952690055663417</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -8625,22 +8625,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2917374181354083</v>
+        <v>0.2936374181354083</v>
       </c>
       <c r="C90">
-        <v>-365.9323634397191</v>
+        <v>-378.291035241891</v>
       </c>
       <c r="D90">
-        <v>399.627636560281</v>
+        <v>396.563964758109</v>
       </c>
       <c r="E90">
-        <v>761.46</v>
+        <v>770.755</v>
       </c>
       <c r="F90">
-        <v>817.96</v>
+        <v>827.255</v>
       </c>
       <c r="G90">
         <v>52.4</v>
@@ -8661,37 +8661,37 @@
         <v>56.95</v>
       </c>
       <c r="M90">
-        <v>192.874968</v>
+        <v>195.066729</v>
       </c>
       <c r="N90">
-        <v>-135.924968</v>
+        <v>-138.116729</v>
       </c>
       <c r="O90">
-        <v>-47.57373880000001</v>
+        <v>-48.34085515</v>
       </c>
       <c r="P90">
-        <v>-88.35122920000003</v>
+        <v>-89.77587385000001</v>
       </c>
       <c r="Q90">
-        <v>-56.55122920000004</v>
+        <v>-57.97587385000001</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.880647858677264</v>
+        <v>0.9565431185570152</v>
       </c>
       <c r="T90">
-        <v>4.10191824767506</v>
+        <v>4.47481990655461</v>
       </c>
       <c r="U90">
         <v>0.2358</v>
       </c>
       <c r="V90">
-        <v>0.1033441519482196</v>
+        <v>0.1021829817016104</v>
       </c>
       <c r="W90">
-        <v>0.2114314489706098</v>
+        <v>0.2117052529147603</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -8699,7 +8699,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.2952690055663417</v>
+        <v>0.2919513762903154</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -8707,22 +8707,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2936374181354083</v>
+        <v>0.2955374181354083</v>
       </c>
       <c r="C91">
-        <v>-378.291035241891</v>
+        <v>-390.6030902697918</v>
       </c>
       <c r="D91">
-        <v>396.563964758109</v>
+        <v>393.5469097302083</v>
       </c>
       <c r="E91">
-        <v>770.755</v>
+        <v>780.0500000000001</v>
       </c>
       <c r="F91">
-        <v>827.255</v>
+        <v>836.5500000000001</v>
       </c>
       <c r="G91">
         <v>52.4</v>
@@ -8743,37 +8743,37 @@
         <v>56.95</v>
       </c>
       <c r="M91">
-        <v>195.066729</v>
+        <v>197.25849</v>
       </c>
       <c r="N91">
-        <v>-138.116729</v>
+        <v>-140.30849</v>
       </c>
       <c r="O91">
-        <v>-48.34085515</v>
+        <v>-49.1079715</v>
       </c>
       <c r="P91">
-        <v>-89.77587385000001</v>
+        <v>-91.20051850000002</v>
       </c>
       <c r="Q91">
-        <v>-57.97587385000001</v>
+        <v>-59.40051850000002</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.9565431185570152</v>
+        <v>1.047617430412717</v>
       </c>
       <c r="T91">
-        <v>4.47481990655461</v>
+        <v>4.922301897210072</v>
       </c>
       <c r="U91">
         <v>0.2358</v>
       </c>
       <c r="V91">
-        <v>0.1021829817016104</v>
+        <v>0.1010476152382592</v>
       </c>
       <c r="W91">
-        <v>0.2117052529147603</v>
+        <v>0.2119729723268185</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -8781,7 +8781,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.2919513762903154</v>
+        <v>0.288707472109312</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -8789,22 +8789,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2955374181354083</v>
+        <v>0.2974374181354084</v>
       </c>
       <c r="C92">
-        <v>-390.6030902697918</v>
+        <v>-402.8695844697723</v>
       </c>
       <c r="D92">
-        <v>393.5469097302083</v>
+        <v>390.5754155302278</v>
       </c>
       <c r="E92">
-        <v>780.0500000000001</v>
+        <v>789.345</v>
       </c>
       <c r="F92">
-        <v>836.5500000000001</v>
+        <v>845.845</v>
       </c>
       <c r="G92">
         <v>52.4</v>
@@ -8825,37 +8825,37 @@
         <v>56.95</v>
       </c>
       <c r="M92">
-        <v>197.25849</v>
+        <v>199.450251</v>
       </c>
       <c r="N92">
-        <v>-140.30849</v>
+        <v>-142.500251</v>
       </c>
       <c r="O92">
-        <v>-49.1079715</v>
+        <v>-49.87508784999999</v>
       </c>
       <c r="P92">
-        <v>-91.20051850000002</v>
+        <v>-92.62516314999999</v>
       </c>
       <c r="Q92">
-        <v>-59.40051850000002</v>
+        <v>-60.82516314999999</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>1.047617430412717</v>
+        <v>1.158930478236352</v>
       </c>
       <c r="T92">
-        <v>4.922301897210072</v>
+        <v>5.469224330233413</v>
       </c>
       <c r="U92">
         <v>0.2358</v>
       </c>
       <c r="V92">
-        <v>0.1010476152382592</v>
+        <v>0.09993720188399262</v>
       </c>
       <c r="W92">
-        <v>0.2119729723268185</v>
+        <v>0.2122348077957546</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -8863,7 +8863,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.288707472109312</v>
+        <v>0.2855348625256933</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -8871,22 +8871,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2974374181354084</v>
+        <v>0.2993374181354083</v>
       </c>
       <c r="C93">
-        <v>-402.8695844697723</v>
+        <v>-415.0915421352916</v>
       </c>
       <c r="D93">
-        <v>390.5754155302278</v>
+        <v>387.6484578647084</v>
       </c>
       <c r="E93">
-        <v>789.345</v>
+        <v>798.64</v>
       </c>
       <c r="F93">
-        <v>845.845</v>
+        <v>855.14</v>
       </c>
       <c r="G93">
         <v>52.4</v>
@@ -8907,37 +8907,37 @@
         <v>56.95</v>
       </c>
       <c r="M93">
-        <v>199.450251</v>
+        <v>201.642012</v>
       </c>
       <c r="N93">
-        <v>-142.500251</v>
+        <v>-144.692012</v>
       </c>
       <c r="O93">
-        <v>-49.87508784999999</v>
+        <v>-50.64220419999999</v>
       </c>
       <c r="P93">
-        <v>-92.62516314999999</v>
+        <v>-94.0498078</v>
       </c>
       <c r="Q93">
-        <v>-60.82516314999999</v>
+        <v>-62.2498078</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>1.158930478236352</v>
+        <v>1.298071788015897</v>
       </c>
       <c r="T93">
-        <v>5.469224330233413</v>
+        <v>6.152877371512592</v>
       </c>
       <c r="U93">
         <v>0.2358</v>
       </c>
       <c r="V93">
-        <v>0.09993720188399262</v>
+        <v>0.09885092795047096</v>
       </c>
       <c r="W93">
-        <v>0.2122348077957546</v>
+        <v>0.2124909511892789</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -8945,7 +8945,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.2855348625256933</v>
+        <v>0.2824312227156314</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -8953,22 +8953,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2993374181354083</v>
+        <v>0.3012374181354084</v>
       </c>
       <c r="C94">
-        <v>-415.0915421352916</v>
+        <v>-427.2699570841247</v>
       </c>
       <c r="D94">
-        <v>387.6484578647084</v>
+        <v>384.7650429158754</v>
       </c>
       <c r="E94">
-        <v>798.64</v>
+        <v>807.9350000000001</v>
       </c>
       <c r="F94">
-        <v>855.14</v>
+        <v>864.4350000000001</v>
       </c>
       <c r="G94">
         <v>52.4</v>
@@ -8989,37 +8989,37 @@
         <v>56.95</v>
       </c>
       <c r="M94">
-        <v>201.642012</v>
+        <v>203.833773</v>
       </c>
       <c r="N94">
-        <v>-144.692012</v>
+        <v>-146.883773</v>
       </c>
       <c r="O94">
-        <v>-50.64220419999999</v>
+        <v>-51.40932055</v>
       </c>
       <c r="P94">
-        <v>-94.0498078</v>
+        <v>-95.47445245000002</v>
       </c>
       <c r="Q94">
-        <v>-62.2498078</v>
+        <v>-63.67445245000002</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>1.298071788015897</v>
+        <v>1.476967757732454</v>
       </c>
       <c r="T94">
-        <v>6.152877371512592</v>
+        <v>7.031859853157249</v>
       </c>
       <c r="U94">
         <v>0.2358</v>
       </c>
       <c r="V94">
-        <v>0.09885092795047096</v>
+        <v>0.09778801474670244</v>
       </c>
       <c r="W94">
-        <v>0.2124909511892789</v>
+        <v>0.2127415861227276</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -9027,7 +9027,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.2824312227156314</v>
+        <v>0.2793943278477213</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -9035,22 +9035,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.3012374181354084</v>
+        <v>0.3031374181354083</v>
       </c>
       <c r="C95">
-        <v>-427.2699570841247</v>
+        <v>-439.4057937834168</v>
       </c>
       <c r="D95">
-        <v>384.7650429158754</v>
+        <v>381.9242062165832</v>
       </c>
       <c r="E95">
-        <v>807.9350000000001</v>
+        <v>817.23</v>
       </c>
       <c r="F95">
-        <v>864.4350000000001</v>
+        <v>873.73</v>
       </c>
       <c r="G95">
         <v>52.4</v>
@@ -9071,37 +9071,37 @@
         <v>56.95</v>
       </c>
       <c r="M95">
-        <v>203.833773</v>
+        <v>206.025534</v>
       </c>
       <c r="N95">
-        <v>-146.883773</v>
+        <v>-149.075534</v>
       </c>
       <c r="O95">
-        <v>-51.40932055</v>
+        <v>-52.1764369</v>
       </c>
       <c r="P95">
-        <v>-95.47445245000002</v>
+        <v>-96.89909710000001</v>
       </c>
       <c r="Q95">
-        <v>-63.67445245000002</v>
+        <v>-65.09909710000001</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>1.476967757732454</v>
+        <v>1.715495717354529</v>
       </c>
       <c r="T95">
-        <v>7.031859853157249</v>
+        <v>8.203836495350124</v>
       </c>
       <c r="U95">
         <v>0.2358</v>
       </c>
       <c r="V95">
-        <v>0.09778801474670244</v>
+        <v>0.09674771671748221</v>
       </c>
       <c r="W95">
-        <v>0.2127415861227276</v>
+        <v>0.2129868883980177</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -9109,7 +9109,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.2793943278477213</v>
+        <v>0.276422047764235</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -9117,22 +9117,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.3031374181354083</v>
+        <v>0.3050374181354083</v>
       </c>
       <c r="C96">
-        <v>-439.4057937834168</v>
+        <v>-451.4999884252663</v>
       </c>
       <c r="D96">
-        <v>381.9242062165832</v>
+        <v>379.1250115747338</v>
       </c>
       <c r="E96">
-        <v>817.23</v>
+        <v>826.5250000000001</v>
       </c>
       <c r="F96">
-        <v>873.73</v>
+        <v>883.0250000000001</v>
       </c>
       <c r="G96">
         <v>52.4</v>
@@ -9153,37 +9153,37 @@
         <v>56.95</v>
       </c>
       <c r="M96">
-        <v>206.025534</v>
+        <v>208.217295</v>
       </c>
       <c r="N96">
-        <v>-149.075534</v>
+        <v>-151.267295</v>
       </c>
       <c r="O96">
-        <v>-52.1764369</v>
+        <v>-52.94355325000001</v>
       </c>
       <c r="P96">
-        <v>-96.89909710000001</v>
+        <v>-98.32374175000004</v>
       </c>
       <c r="Q96">
-        <v>-65.09909710000001</v>
+        <v>-66.52374175000004</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>1.715495717354529</v>
+        <v>2.049434860825436</v>
       </c>
       <c r="T96">
-        <v>8.203836495350124</v>
+        <v>9.844603794420154</v>
       </c>
       <c r="U96">
         <v>0.2358</v>
       </c>
       <c r="V96">
-        <v>0.09674771671748221</v>
+        <v>0.09572931969940343</v>
       </c>
       <c r="W96">
-        <v>0.2129868883980177</v>
+        <v>0.2132270264148807</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.276422047764235</v>
+        <v>0.2735123419982954</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -9199,22 +9199,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.3050374181354083</v>
+        <v>0.3069374181354083</v>
       </c>
       <c r="C97">
-        <v>-451.4999884252663</v>
+        <v>-463.5534499553503</v>
       </c>
       <c r="D97">
-        <v>379.1250115747338</v>
+        <v>376.3665500446498</v>
       </c>
       <c r="E97">
-        <v>826.5250000000001</v>
+        <v>835.8200000000001</v>
       </c>
       <c r="F97">
-        <v>883.0250000000001</v>
+        <v>892.3200000000001</v>
       </c>
       <c r="G97">
         <v>52.4</v>
@@ -9235,37 +9235,37 @@
         <v>56.95</v>
       </c>
       <c r="M97">
-        <v>208.217295</v>
+        <v>210.409056</v>
       </c>
       <c r="N97">
-        <v>-151.267295</v>
+        <v>-153.459056</v>
       </c>
       <c r="O97">
-        <v>-52.94355325000001</v>
+        <v>-53.71066960000001</v>
       </c>
       <c r="P97">
-        <v>-98.32374175000004</v>
+        <v>-99.74838640000002</v>
       </c>
       <c r="Q97">
-        <v>-66.52374175000004</v>
+        <v>-67.94838640000002</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>2.049434860825436</v>
+        <v>2.550343576031796</v>
       </c>
       <c r="T97">
-        <v>9.844603794420154</v>
+        <v>12.3057547430252</v>
       </c>
       <c r="U97">
         <v>0.2358</v>
       </c>
       <c r="V97">
-        <v>0.09572931969940343</v>
+        <v>0.09473213928586798</v>
       </c>
       <c r="W97">
-        <v>0.2132270264148807</v>
+        <v>0.2134621615563923</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -9273,7 +9273,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.2735123419982954</v>
+        <v>0.2706632551024799</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -9281,22 +9281,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.3069374181354083</v>
+        <v>0.3088374181354083</v>
       </c>
       <c r="C98">
-        <v>-463.5534499553502</v>
+        <v>-475.567061056972</v>
       </c>
       <c r="D98">
-        <v>376.3665500446498</v>
+        <v>373.6479389430281</v>
       </c>
       <c r="E98">
-        <v>835.8199999999999</v>
+        <v>845.115</v>
       </c>
       <c r="F98">
-        <v>892.3199999999999</v>
+        <v>901.615</v>
       </c>
       <c r="G98">
         <v>52.4</v>
@@ -9317,37 +9317,37 @@
         <v>56.95</v>
       </c>
       <c r="M98">
-        <v>210.409056</v>
+        <v>212.600817</v>
       </c>
       <c r="N98">
-        <v>-153.459056</v>
+        <v>-155.650817</v>
       </c>
       <c r="O98">
-        <v>-53.71066959999999</v>
+        <v>-54.47778595</v>
       </c>
       <c r="P98">
-        <v>-99.74838639999999</v>
+        <v>-101.17303105</v>
       </c>
       <c r="Q98">
-        <v>-67.94838639999999</v>
+        <v>-69.37303105000002</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>2.550343576031789</v>
+        <v>3.385191434709053</v>
       </c>
       <c r="T98">
-        <v>12.30575474302517</v>
+        <v>16.40767299070022</v>
       </c>
       <c r="U98">
         <v>0.2358</v>
       </c>
       <c r="V98">
-        <v>0.094732139285868</v>
+        <v>0.09375551929323017</v>
       </c>
       <c r="W98">
-        <v>0.2134621615563923</v>
+        <v>0.2136924485506563</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -9355,7 +9355,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.2706632551024801</v>
+        <v>0.2678729122663719</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -9363,22 +9363,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.3088374181354083</v>
+        <v>0.3107374181354083</v>
       </c>
       <c r="C99">
-        <v>-475.567061056972</v>
+        <v>-487.5416790927637</v>
       </c>
       <c r="D99">
-        <v>373.6479389430281</v>
+        <v>370.9683209072363</v>
       </c>
       <c r="E99">
-        <v>845.115</v>
+        <v>854.41</v>
       </c>
       <c r="F99">
-        <v>901.615</v>
+        <v>910.91</v>
       </c>
       <c r="G99">
         <v>52.4</v>
@@ -9399,37 +9399,37 @@
         <v>56.95</v>
       </c>
       <c r="M99">
-        <v>212.600817</v>
+        <v>214.792578</v>
       </c>
       <c r="N99">
-        <v>-155.650817</v>
+        <v>-157.842578</v>
       </c>
       <c r="O99">
-        <v>-54.47778595</v>
+        <v>-55.2449023</v>
       </c>
       <c r="P99">
-        <v>-101.17303105</v>
+        <v>-102.5976757</v>
       </c>
       <c r="Q99">
-        <v>-69.37303105000002</v>
+        <v>-70.7976757</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>3.385191434709053</v>
+        <v>5.054887152063579</v>
       </c>
       <c r="T99">
-        <v>16.40767299070022</v>
+        <v>24.61150948605033</v>
       </c>
       <c r="U99">
         <v>0.2358</v>
       </c>
       <c r="V99">
-        <v>0.09375551929323017</v>
+        <v>0.09279883032085029</v>
       </c>
       <c r="W99">
-        <v>0.2136924485506563</v>
+        <v>0.2139180358103435</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -9437,7 +9437,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.2678729122663719</v>
+        <v>0.2651395152024294</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -9445,22 +9445,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.3107374181354083</v>
+        <v>0.3126374181354083</v>
       </c>
       <c r="C100">
-        <v>-487.5416790927637</v>
+        <v>-499.478137006159</v>
       </c>
       <c r="D100">
-        <v>370.9683209072363</v>
+        <v>368.3268629938411</v>
       </c>
       <c r="E100">
-        <v>854.41</v>
+        <v>863.705</v>
       </c>
       <c r="F100">
-        <v>910.91</v>
+        <v>920.205</v>
       </c>
       <c r="G100">
         <v>52.4</v>
@@ -9481,37 +9481,37 @@
         <v>56.95</v>
       </c>
       <c r="M100">
-        <v>214.792578</v>
+        <v>216.984339</v>
       </c>
       <c r="N100">
-        <v>-157.842578</v>
+        <v>-160.034339</v>
       </c>
       <c r="O100">
-        <v>-55.2449023</v>
+        <v>-56.01201864999999</v>
       </c>
       <c r="P100">
-        <v>-102.5976757</v>
+        <v>-104.02232035</v>
       </c>
       <c r="Q100">
-        <v>-70.7976757</v>
+        <v>-72.22232035</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>5.054887152063579</v>
+        <v>10.06397430412716</v>
       </c>
       <c r="T100">
-        <v>24.61150948605033</v>
+        <v>49.22301897210066</v>
       </c>
       <c r="U100">
         <v>0.2358</v>
       </c>
       <c r="V100">
-        <v>0.09279883032085029</v>
+        <v>0.09186146839841745</v>
       </c>
       <c r="W100">
-        <v>0.2139180358103435</v>
+        <v>0.2141390657516532</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -9519,91 +9519,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.2651395152024294</v>
+        <v>0.2624613382811928</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.3126374181354083</v>
-      </c>
-      <c r="C101">
-        <v>-499.478137006159</v>
-      </c>
-      <c r="D101">
-        <v>368.3268629938411</v>
-      </c>
-      <c r="E101">
-        <v>863.705</v>
-      </c>
-      <c r="F101">
-        <v>920.205</v>
-      </c>
-      <c r="G101">
-        <v>52.4</v>
-      </c>
-      <c r="H101">
-        <v>873</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>88.75</v>
-      </c>
-      <c r="K101">
-        <v>31.8</v>
-      </c>
-      <c r="L101">
-        <v>56.95</v>
-      </c>
-      <c r="M101">
-        <v>216.984339</v>
-      </c>
-      <c r="N101">
-        <v>-160.034339</v>
-      </c>
-      <c r="O101">
-        <v>-56.01201864999999</v>
-      </c>
-      <c r="P101">
-        <v>-104.02232035</v>
-      </c>
-      <c r="Q101">
-        <v>-72.22232035</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>10.06397430412716</v>
-      </c>
-      <c r="T101">
-        <v>49.22301897210066</v>
-      </c>
-      <c r="U101">
-        <v>0.2358</v>
-      </c>
-      <c r="V101">
-        <v>0.09186146839841745</v>
-      </c>
-      <c r="W101">
-        <v>0.2141390657516532</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>D2/D</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.2624613382811928</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
